--- a/workspaces/btc_daily_14days/volatility/realized_vol_21.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_21.xlsx
@@ -575,46 +575,46 @@
         <v>106</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.110335264695685</v>
+        <v>4.096039652685292</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10.99212144956936</v>
+        <v>10.95580256824146</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.54377637919832</v>
+        <v>11.50528877476728</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.62120102134528</v>
+        <v>12.57918305818534</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>14.91856955286107</v>
+        <v>14.86885261162733</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>14.27567247555791</v>
+        <v>14.22795017294051</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>18.91851303118872</v>
+        <v>18.85579264054723</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>19.4005065572833</v>
+        <v>19.33601063959191</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>21.23479650615166</v>
+        <v>21.16455433206342</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>20.3882217702787</v>
+        <v>20.32065585564281</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>19.24237752257967</v>
+        <v>19.17857130546415</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>18.33590559393089</v>
+        <v>18.27489677605585</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>19.81147897507372</v>
+        <v>19.74576572449231</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>20.06711142690892</v>
+        <v>20.00054192219847</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>197</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.224402787215162</v>
+        <v>-1.221510975425389</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.31336907296852</v>
+        <v>-1.310310011988349</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.200730604950593</v>
+        <v>-1.198505323668563</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.977582632551623</v>
+        <v>1.968775242009855</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.43939935973598</v>
+        <v>1.432020504496236</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.26268248226647</v>
+        <v>3.248983180500346</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.721085640935677</v>
+        <v>5.698693634568635</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.272013313421255</v>
+        <v>6.24746668177503</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.721406555809814</v>
+        <v>6.695412515638075</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.941869166086335</v>
+        <v>9.904789667448583</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.230378353376295</v>
+        <v>9.195867062354736</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.722130986834649</v>
+        <v>6.696145536148201</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.811783581251241</v>
+        <v>6.785479509944693</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.101901350844088</v>
+        <v>9.06768108511325</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>234</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.207416380644823</v>
+        <v>2.198088615567691</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.823650091614162</v>
+        <v>-2.814687365228352</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.219350855986164</v>
+        <v>-3.209461117252495</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.089580237268144</v>
+        <v>-3.080896184590877</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.629163964176399</v>
+        <v>-3.618872761201672</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.759890826103891</v>
+        <v>-3.749530095763106</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.273296893819968</v>
+        <v>-4.261798785166846</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.454854911493648</v>
+        <v>-6.435763986452116</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.232530858129799</v>
+        <v>-5.217894367147004</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.228631471731525</v>
+        <v>-5.214644403906043</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-5.435253618040342</v>
+        <v>-5.420235788408689</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.40223940886883</v>
+        <v>-5.386968988634614</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.253871971386651</v>
+        <v>-6.23551093493063</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.71739477452671</v>
+        <v>-4.705150708022984</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>261</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.685009201436031</v>
+        <v>-2.676397705912876</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.148049422636895</v>
+        <v>-3.136454779929821</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.69409912576652</v>
+        <v>-4.676889694763958</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.098816803065475</v>
+        <v>-6.07692755530595</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.488666770867958</v>
+        <v>-5.469474204766946</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.575807433253871</v>
+        <v>-5.556707202483885</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.045676687549403</v>
+        <v>-6.025439983670424</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.59568047625762</v>
+        <v>-4.581066211727659</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.273699520621911</v>
+        <v>-4.260650543128165</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.279236756354265</v>
+        <v>-6.258990118190013</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.486461609243456</v>
+        <v>-6.465026647752545</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.300691370932533</v>
+        <v>-5.28352352566084</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.416714404045599</v>
+        <v>-3.406806632592428</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.935125426833622</v>
+        <v>-3.924130961485815</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>247</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2667176724366911</v>
+        <v>-0.2670056014948088</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.17099993544339</v>
+        <v>2.161793011836949</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.397087713136976</v>
+        <v>3.382582892920851</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.339228052070538</v>
+        <v>4.320152207671292</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.396341470692818</v>
+        <v>3.380757554202361</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.317759279521297</v>
+        <v>5.293481197225063</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.263338221005611</v>
+        <v>7.230060637400037</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>8.826800525724181</v>
+        <v>8.786476215231154</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.333470600809498</v>
+        <v>6.303354721015623</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.889325938381496</v>
+        <v>5.860935278668748</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.842343382654796</v>
+        <v>2.827479263429737</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.503235552837054</v>
+        <v>4.481360391002326</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.89631818395155</v>
+        <v>4.872343589161567</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.743319293604344</v>
+        <v>4.719050821441797</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>257</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.3159002011908</v>
+        <v>4.294161428525683</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.537620344112078</v>
+        <v>1.529704241335061</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.971919314465573</v>
+        <v>-1.963979212997131</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.452381474879843</v>
+        <v>-1.447866551221125</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4331796156515111</v>
+        <v>-0.4337026556294674</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.693883421893979</v>
+        <v>-1.689815526589243</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.338181527923176</v>
+        <v>-3.327979278698912</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.636520117355765</v>
+        <v>-2.630616081630762</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.7472746508080164</v>
+        <v>-0.7497787185130846</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4288374045724339</v>
+        <v>-0.4328648347725803</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.5361563825191311</v>
+        <v>0.5293701781333482</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.209651398898302</v>
+        <v>-0.2134797041211556</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.021622006449583</v>
+        <v>-1.022302769809734</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.160540538014246</v>
+        <v>-1.161634129486856</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.480280425473055</v>
+        <v>-3.506457415500982</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4866604457326389</v>
+        <v>-0.4883263001473921</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.080837199252862</v>
+        <v>2.102035633933959</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8950924792506569</v>
+        <v>0.9075614421496141</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.6318560380866387</v>
+        <v>-0.6325930286319021</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.651914350817492</v>
+        <v>-1.660697423426626</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.736713557517994</v>
+        <v>-1.744294160277171</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.874798433958922</v>
+        <v>-1.880779003106177</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.566126292011809</v>
+        <v>-5.607000668270736</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.779759052129791</v>
+        <v>-3.803018341153198</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.15336520781176</v>
+        <v>-2.164006718115353</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.9464771550378757</v>
+        <v>-0.9449447307741607</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4681917173402681</v>
+        <v>0.4841148986876505</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.8964486650940415</v>
+        <v>0.9187809159087337</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.645414004100623</v>
+        <v>-2.707526021822915</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.181571139933453</v>
+        <v>-3.262812457579194</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.499174118431696</v>
+        <v>-2.558673012652207</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.03088800342487</v>
+        <v>-4.128660611725209</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.399089767946094</v>
+        <v>-4.507453003334092</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.422463958079099</v>
+        <v>-2.472854259267244</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.953578763298438</v>
+        <v>-3.012589895486549</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-4.773827499195733</v>
+        <v>-4.874917754192793</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.228766701934724</v>
+        <v>-2.268553115234859</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-6.240877577408497</v>
+        <v>-6.38614897178384</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.435667299625557</v>
+        <v>-6.590902296101348</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.496072440336967</v>
+        <v>-5.619019138755988</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.607947415900441</v>
+        <v>-5.72677374970074</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.157919549100441</v>
+        <v>-4.227052417424673</v>
       </c>
     </row>
     <row r="14">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 15.49</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4073~4086</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4073</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2663213353837364</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 18.98</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3967~3980</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3967</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.3828855563908817</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 22.47</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3770~3783</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3770</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.3390634854227628</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 25.95</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3536~3549</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3536</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.5069632568118365</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 29.44</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3275~3288</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3275</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.3340709236163022</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 32.93</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3028~3041</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3028</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.3395415757180302</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 36.42</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2771~2784</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2771</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.7693003891754913</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 39.91</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2471~2480</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2471</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.4369867073067581</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 43.4</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2151~2151</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2151</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.09920308078645235</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 46.88</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1867~1867</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1867</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.9077400407969876</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 50.37</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1599~1599</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1599</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.7898637435799003</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 53.86</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1394~1394</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1394</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.5194741618560244</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 57.35</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1176~1176</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1176</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.05758208795328557</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 60.84</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1036~1036</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1036</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.2092643824927194</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 64.33</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>891~891</t>
-        </is>
+      <c r="B20" t="n">
+        <v>891</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.0804192405242361</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 67.81</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>799~799</t>
-        </is>
+      <c r="B21" t="n">
+        <v>799</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.303200522963408</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 71.3</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>696~696</t>
-        </is>
+      <c r="B22" t="n">
+        <v>696</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.344013032853653</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 74.79</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>597~597</t>
-        </is>
+      <c r="B23" t="n">
+        <v>597</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.739669475988869</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 78.28</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>501~501</t>
-        </is>
+      <c r="B24" t="n">
+        <v>501</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-2.393637921008377</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 81.77</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>397~397</t>
-        </is>
+      <c r="B25" t="n">
+        <v>397</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.35238038570116</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 85.26</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>322~322</t>
-        </is>
+      <c r="B26" t="n">
+        <v>322</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.251202295365253</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 88.74</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>275~275</t>
-        </is>
+      <c r="B27" t="n">
+        <v>275</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-2.675256502028155</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 92.23</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>240~240</t>
-        </is>
+      <c r="B28" t="n">
+        <v>240</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-2.076771653543311</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 95.72</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>215~215</t>
-        </is>
+      <c r="B29" t="n">
+        <v>215</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-3.656229017884399</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 99.21</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>183~183</t>
-        </is>
+      <c r="B30" t="n">
+        <v>183</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-2.220214276494126</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 102.7</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>173~173</t>
-        </is>
+      <c r="B31" t="n">
+        <v>173</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-2.204420979169512</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 106.2</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>153~153</t>
-        </is>
+      <c r="B32" t="n">
+        <v>153</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.513046163347234</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 109.7</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>141~141</t>
-        </is>
+      <c r="B33" t="n">
+        <v>141</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.7203886748199082</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 113.2</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>124~124</t>
-        </is>
+      <c r="B34" t="n">
+        <v>124</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.8805350944035268</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 116.6</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-3.683914510686165</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 15.49</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>12.98275215598051</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 18.98</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>190~190</t>
-        </is>
+      <c r="B7" t="n">
+        <v>190</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>8.03287746926371</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 22.47</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>387~387</t>
-        </is>
+      <c r="B8" t="n">
+        <v>387</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3.320515168162117</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 25.95</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>621~621</t>
-        </is>
+      <c r="B9" t="n">
+        <v>621</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>2.90108663953238</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 29.44</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>882~882</t>
-        </is>
+      <c r="B10" t="n">
+        <v>882</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1.248058278429482</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 32.93</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1129~1129</t>
-        </is>
+      <c r="B11" t="n">
+        <v>1129</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.9166591111452078</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 36.42</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1386~1386</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1386</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.546965720194066</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 39.91</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1686~1690</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1686</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.6426563543462365</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 43.4</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2006~2019</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2006</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.1068588566102378</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 46.88</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2290~2303</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2290</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.7348625494761478</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 50.37</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2558~2571</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2558</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.4903266904939159</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 53.86</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2763~2776</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2763</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.2600089253972939</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 57.35</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2981~2994</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2981</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.02182843377043753</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 60.84</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3121~3134</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3121</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.06842236615764108</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 64.33</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3266~3279</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3266</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.02257265874702341</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 67.81</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3358~3371</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3358</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.07256583286032736</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 71.3</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3461~3474</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3461</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.2699468265948539</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 74.79</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3560~3573</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3560</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.2913363789224093</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 78.28</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3656~3669</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3656</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.3274938138865124</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 81.77</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3760~3773</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3760</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.03770400685072417</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 85.26</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3835~3848</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3835</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.1053142785426218</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 88.74</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3882~3895</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3882</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.1894885090583216</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 92.23</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3917~3930</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3917</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.1274268197391351</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 95.72</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3942~3955</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3942</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.1993556115220088</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 99.21</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3974~3987</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3974</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.1024984743724104</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 102.7</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3984~3997</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3984</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.09600376135119149</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 106.2</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4004~4017</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4004</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.05821714406685174</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 109.7</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4016~4029</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4016</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.02579722210820989</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 113.2</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4033~4046</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4033</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.02757008315137455</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 116.6</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4073~4086</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4073</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.07631204689721471</v>

--- a/workspaces/btc_daily_14days/volatility/realized_vol_21.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_21.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-21 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-21 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>106</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.096039652685292</v>
+        <v>4.108523803877361</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10.95580256824146</v>
+        <v>10.96868097066127</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.50528877476728</v>
+        <v>11.51826737008331</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.57918305818534</v>
+        <v>12.5921370089178</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>14.86885261162733</v>
+        <v>14.88194180534764</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>14.22795017294051</v>
+        <v>14.24097370212137</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>18.85579264054723</v>
+        <v>18.86884391167197</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>19.33601063959191</v>
+        <v>19.34917885411783</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>21.16455433206342</v>
+        <v>21.1777429161851</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>20.32065585564281</v>
+        <v>20.33405244352736</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>19.17857130546415</v>
+        <v>19.19202193280601</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>18.27489677605585</v>
+        <v>18.28834451974179</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>19.74576572449231</v>
+        <v>19.7593195599172</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>20.00054192219847</v>
+        <v>19.99011228650031</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>197</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.221510975425389</v>
+        <v>-1.20903442026448</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.310310011988349</v>
+        <v>-1.297443733607537</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.198505323668563</v>
+        <v>-1.185538123329714</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.968775242009855</v>
+        <v>1.981720417374191</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.432020504496236</v>
+        <v>1.44510021170602</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.248983180500346</v>
+        <v>3.261999616410826</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.698693634568635</v>
+        <v>5.711737956199627</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.24746668177503</v>
+        <v>6.260628988186589</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.695412515638075</v>
+        <v>6.708595777877086</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.904789667448583</v>
+        <v>9.918183085005793</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.195867062354736</v>
+        <v>9.209315363179172</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.696145536148201</v>
+        <v>6.709591486738013</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.785479509944693</v>
+        <v>6.799032364089925</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.06768108511325</v>
+        <v>9.057251449415098</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>234</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.198088615567691</v>
+        <v>2.210563060306058</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.814687365228352</v>
+        <v>-2.801827908905018</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.209461117252495</v>
+        <v>-3.196500595494889</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.080896184590877</v>
+        <v>-3.067958929934029</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.618872761201672</v>
+        <v>-3.605800283545335</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.749530095763106</v>
+        <v>-3.73652105353338</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.261798785166846</v>
+        <v>-4.248762279987204</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.435763986452116</v>
+        <v>-6.422609639778983</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.217894367147004</v>
+        <v>-5.20471740010619</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.214644403906043</v>
+        <v>-5.201256849054317</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-5.420235788408689</v>
+        <v>-5.406791811237049</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.386968988634614</v>
+        <v>-5.373525603399962</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.23551093493063</v>
+        <v>-6.221959440767925</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.705150708022984</v>
+        <v>-4.715580343721037</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>261</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.676397705912876</v>
+        <v>-2.663935916238088</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.136454779929821</v>
+        <v>-3.123603643047254</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.676889694763958</v>
+        <v>-4.663938076373</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.07692755530595</v>
+        <v>-6.063999701827726</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.469474204766946</v>
+        <v>-5.456409378315058</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.556707202483885</v>
+        <v>-5.543704900789038</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.025439983670424</v>
+        <v>-6.012409397227437</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.581066211727659</v>
+        <v>-4.567915256842255</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.260650543128165</v>
+        <v>-4.247476674689594</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.258990118190013</v>
+        <v>-6.245605802532936</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.465026647752545</v>
+        <v>-6.451585132478854</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.28352352566084</v>
+        <v>-5.270081573964191</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.406806632592428</v>
+        <v>-3.39325562762162</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.924130961485815</v>
+        <v>-3.93456059718406</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>247</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2670056014948088</v>
+        <v>-0.2545509895240841</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.161793011836949</v>
+        <v>2.174640661615669</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.382582892920851</v>
+        <v>3.395534062139589</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.320152207671292</v>
+        <v>4.333081856752578</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.380757554202361</v>
+        <v>3.393822617402243</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.293481197225063</v>
+        <v>5.306485498356906</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.230060637400037</v>
+        <v>7.243094746937054</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>8.786476215231154</v>
+        <v>8.799630494210611</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.303354721015623</v>
+        <v>6.316529897181816</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.860935278668748</v>
+        <v>5.874321042670502</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.827479263429737</v>
+        <v>2.840920897854268</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.481360391002326</v>
+        <v>4.494802591926451</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.872343589161567</v>
+        <v>4.885894609087224</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.719050821441797</v>
+        <v>4.708621185743645</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>257</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.294161428525683</v>
+        <v>4.106289718082913</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.529704241335061</v>
+        <v>1.542540210056089</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.963979212997131</v>
+        <v>-1.951045002744927</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.447866551221125</v>
+        <v>-1.434952391491684</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4337026556294674</v>
+        <v>-0.4206496313766692</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.689815526589243</v>
+        <v>-1.676824497270424</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.327979278698912</v>
+        <v>-3.314959423634086</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.630616081630762</v>
+        <v>-2.617474332614968</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.7497787185130846</v>
+        <v>-0.7366116430216607</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4328648347725803</v>
+        <v>-0.4194852867864398</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.5293701781333482</v>
+        <v>0.5428082967328436</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2134797041211556</v>
+        <v>-0.2000403368986525</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.022302769809734</v>
+        <v>-1.00875330962117</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.161634129486856</v>
+        <v>-1.172063765185008</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.506457415500982</v>
+        <v>-3.484841580887363</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4883263001473921</v>
+        <v>-0.474646035438262</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.102035633933959</v>
+        <v>2.106918610543438</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.9075614421496141</v>
+        <v>0.9158226417580835</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.6325930286319021</v>
+        <v>-0.6190482160843302</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.660697423426626</v>
+        <v>-1.644080111021339</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.744294160277171</v>
+        <v>-1.728114120230849</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.880779003106177</v>
+        <v>-1.865098853339063</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.607000668270736</v>
+        <v>-5.577702629291444</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.803018341153198</v>
+        <v>-3.780364310301408</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.164006718115353</v>
+        <v>-2.330133114090899</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.9449447307741607</v>
+        <v>-1.115078224042698</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4841148986876505</v>
+        <v>0.3078756619565439</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.9187809159087337</v>
+        <v>1.05010100335565</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>320</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.707526021822915</v>
+        <v>-2.695003732147292</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.262812457579194</v>
+        <v>-3.417454946178765</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.558673012652207</v>
+        <v>-2.714233330862264</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.128660611725209</v>
+        <v>-4.283378590753507</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.507453003334092</v>
+        <v>-4.66381155532526</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.472854259267244</v>
+        <v>-2.628157587740802</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.012589895486549</v>
+        <v>-3.167501520218941</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-4.874917754192793</v>
+        <v>-5.030229107931639</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.268553115234859</v>
+        <v>-2.425246196203815</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-6.38614897178384</v>
+        <v>-6.54454299461645</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.590902296101348</v>
+        <v>-6.57744500239113</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.619019138755988</v>
+        <v>-5.605566850035878</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.72677374970074</v>
+        <v>-5.713217703349137</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.227052417424673</v>
+        <v>-4.237482053122825</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>284</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-6.718790432886031</v>
+        <v>-6.706268143210409</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.55621866793976</v>
+        <v>-5.543211536522158</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-5.778078211388674</v>
+        <v>-5.76509906899021</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.260161398291828</v>
+        <v>-5.247050593916889</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-6.019057488745183</v>
+        <v>-6.006014592450818</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.399565853904782</v>
+        <v>-5.386499599604306</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.866749252686205</v>
+        <v>-5.853568243390967</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.984087167037764</v>
+        <v>-6.970888428083001</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-8.890550380234544</v>
+        <v>-8.877145252581712</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-9.79952905666488</v>
+        <v>-9.786071762954663</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-11.17359660354472</v>
+        <v>-11.16014431482461</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-9.481175158151594</v>
+        <v>-9.467619111799991</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-8.527228473762548</v>
+        <v>-8.5376581094607</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>268</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.611039291730286</v>
+        <v>1.623561581405909</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3726000071243192</v>
+        <v>0.3855098167003703</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.02226869947239862</v>
+        <v>-0.009261568054796498</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.757687208655945</v>
+        <v>-1.744708066257481</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.803571110295195</v>
+        <v>-0.7904603059202557</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.8792635009376966</v>
+        <v>-0.8662206046433312</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5908628898518131</v>
+        <v>-0.5777966355513371</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.06135669644135078</v>
+        <v>0.07453770573658858</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.865314831531947</v>
+        <v>-1.852116092577184</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.8497683747689138</v>
+        <v>-0.8363632471160827</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.80079035580291</v>
+        <v>-1.787333062092692</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.766407198457479</v>
+        <v>-1.752954909737369</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.440393152686049</v>
+        <v>-1.426837106334446</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.802612118917139</v>
+        <v>-3.813041754615291</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>205</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.628512899302279</v>
+        <v>2.641035188977902</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.504744164386693</v>
+        <v>1.517653973962744</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.524509604131616</v>
+        <v>4.537516735549218</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.679152980641554</v>
+        <v>3.692132123040018</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.165122009471823</v>
+        <v>2.178232813846762</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.464265321105195</v>
+        <v>-0.4512224248108296</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.4266107177201448</v>
+        <v>0.4396769720206208</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.910646831133647</v>
+        <v>1.923827840428885</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.877570540411341</v>
+        <v>5.890975668064172</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>8.111841606337606</v>
+        <v>8.125298900047824</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8.146224763683037</v>
+        <v>8.159677052403147</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.79914088444545</v>
+        <v>4.812696930797053</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.073252460624232</v>
+        <v>4.06282282492608</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>218</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.011148835753382</v>
+        <v>3.023671125429004</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.069299993431272</v>
+        <v>5.082209803007324</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.757000094174124</v>
+        <v>3.770007225591726</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.052390841460578</v>
+        <v>2.065369983859043</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1378228373975361</v>
+        <v>0.1509336417724754</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.399597610207955</v>
+        <v>-1.38655471391359</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.319193712801393</v>
+        <v>-3.306127458500917</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.951514726261635</v>
+        <v>-1.938333716966397</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.599670575746735</v>
+        <v>-6.586471836791972</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.862639797472021</v>
+        <v>-2.849234669819189</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.984824314450044</v>
+        <v>-3.971367020739827</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.19814757912296</v>
+        <v>-1.18469529040285</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.15968659373759</v>
+        <v>-1.146130547385987</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.744827646782497</v>
+        <v>-2.755257282480649</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>140</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.064866891638552</v>
+        <v>-1.052344601962929</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.390726218888524</v>
+        <v>-3.377816409312473</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.928452068342253</v>
+        <v>-5.915444936924651</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.941056078591977</v>
+        <v>-2.928076936193513</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.6223344365212853</v>
+        <v>-0.609223632146346</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.75346392737697</v>
+        <v>-1.740421031082604</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.266769073220686</v>
+        <v>-3.25370281892021</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.305381043430828</v>
+        <v>-2.29220003413559</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.20504764181544</v>
+        <v>1.218246380770204</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>6.069208171073385</v>
+        <v>6.082613298726216</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>8.721597703898667</v>
+        <v>8.735054997608884</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>10.18455228981536</v>
+        <v>10.19800457853547</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.192869107441965</v>
+        <v>6.206425153793568</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.014019011146829</v>
+        <v>5.003589375448676</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>145</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.989320300479648</v>
+        <v>2.00184259015527</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>6.584643239239561</v>
+        <v>6.597553048815612</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.01712201908119937</v>
+        <v>-0.004114887663597244</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.266179231301258</v>
+        <v>-1.253200088902794</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4252901015457198</v>
+        <v>-0.4121792971707805</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.507158508657767</v>
+        <v>-1.494115612363402</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.591892225929961</v>
+        <v>-1.578825971629485</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.768510582185016</v>
+        <v>2.781691591480254</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.328200351175234</v>
+        <v>1.341399090129997</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.9629770142432932</v>
+        <v>0.9764343079535109</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.37667051641651</v>
+        <v>2.39012280513662</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.266760733057737</v>
+        <v>1.28031677940934</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.242138624321079</v>
+        <v>-1.252568260019231</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>92</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.85438776674642</v>
+        <v>1.866910056422043</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.0180554114351</v>
+        <v>-3.005145601859049</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.239011074553375</v>
+        <v>-1.226003943135773</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.195714463685064</v>
+        <v>-2.1827353212866</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.734135678757291</v>
+        <v>-2.721024874382351</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.91113234591495</v>
+        <v>1.924175242209316</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.7394421069035459</v>
+        <v>0.752508361204022</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2722587081220453</v>
+        <v>0.2854397174172831</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.211258821939623</v>
+        <v>0.2244575608943862</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.191445774362158</v>
+        <v>-5.177988480651941</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.33097566049512</v>
+        <v>-7.31752337177501</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.751230271439958</v>
+        <v>-7.737674225088355</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-10.76237850438119</v>
+        <v>-10.77280814007934</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>103</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>6.729862650663861</v>
+        <v>6.742384940339484</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.205667678476253</v>
+        <v>2.218577488052304</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.810798971879663</v>
+        <v>1.823806103297265</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.970178318079391</v>
+        <v>0.9831574604778552</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.28612603504606</v>
+        <v>5.299236839420999</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.554441759169485</v>
+        <v>6.567484655463851</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.52796046908167</v>
+        <v>4.541026723382146</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.031650856707941</v>
+        <v>5.044831866003179</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>6.912398543341283</v>
+        <v>6.925597282296046</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.14965199908994</v>
+        <v>3.163057126742771</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.974024888364539</v>
+        <v>1.987482182074757</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.06666047289444066</v>
+        <v>0.08011276161455072</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.529901007580605</v>
+        <v>3.543457053932208</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.779622339856999</v>
+        <v>3.769192704158847</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>99</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.041915215143561</v>
+        <v>1.054437504819184</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4404426122803073</v>
+        <v>0.4533524218563585</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>7.11628097639079</v>
+        <v>7.129288107808392</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.216231078695266</v>
+        <v>4.22921022109373</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3494833724060129</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.095455269368315</v>
+        <v>-3.08241237307395</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.159986966438574</v>
+        <v>-1.146920712138098</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>0.4062126642771844</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6780692413014293</v>
+        <v>-0.6648705023466661</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.588800486935355</v>
+        <v>-7.575395359282524</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.773351791050914</v>
+        <v>-5.759894497340696</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.749069643806436</v>
+        <v>-6.735617355086326</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-7.169324254751395</v>
+        <v>-7.155768208399792</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.899400902273086</v>
+        <v>-4.909830537971239</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>96</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.673228346456689</v>
+        <v>1.685750636132312</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.10332140015916</v>
+        <v>1.116231209735211</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.791786026895842</v>
+        <v>2.804793158313444</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.047039159503342</v>
+        <v>6.060018301901806</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.341951277764508</v>
+        <v>1.355062082139447</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>5.806059882146776</v>
+        <v>5.819102778441142</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.762992831541226</v>
+        <v>6.776059085841702</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.129142766093054</v>
+        <v>2.142323775388292</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.151476213244145</v>
+        <v>4.164674952198908</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.343017694882825</v>
+        <v>4.356422822535656</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.054931037231974</v>
+        <v>2.068388330942192</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>0.01943314996412226</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.752392916965775</v>
+        <v>3.765948963317378</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.960447582575398</v>
+        <v>2.950017946877246</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>104</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-10.18574601251767</v>
+        <v>-10.17322372284205</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-6.028088856251209</v>
+        <v>-6.015179046675158</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-7.384496024386209</v>
+        <v>-7.371488892968607</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.023433337620105</v>
+        <v>-2.010322533245166</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7644529383659346</v>
+        <v>-0.7514100420715693</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.772263578715183</v>
+        <v>-2.759197324414707</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-6.124062362112099</v>
+        <v>-6.110881352816861</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.261985325217509</v>
+        <v>-4.248786586262746</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.150572048706913</v>
+        <v>-4.137166921054082</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.239940757639935</v>
+        <v>-7.226483463929718</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.856581442008576</v>
+        <v>-1.843025395656973</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.3162168133446244</v>
+        <v>0.3057871776464722</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>75</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.506561679790032</v>
+        <v>3.519083969465655</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.894988066825775</v>
+        <v>1.907897876401826</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1667860268958421</v>
+        <v>0.1797931583134442</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.2970391595033419</v>
+        <v>0.3100183019018061</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.758617944431144</v>
+        <v>3.771728748806083</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>1.402436111774541</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.971326164874554</v>
+        <v>3.98439241917503</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.170809432759761</v>
+        <v>2.183990442054998</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.443142879910752</v>
+        <v>3.456341618865515</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>3.939756155868992</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.05493103723191</v>
+        <v>5.068388330942128</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.577352472089316</v>
+        <v>-5.563900183369206</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-8.664273749700889</v>
+        <v>-8.650717703349287</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-11.0812190840913</v>
+        <v>-11.09164871978945</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>47</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.081029764896407</v>
+        <v>7.093552054572029</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>9.724775300868323</v>
+        <v>9.737685110444374</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.202247019803593</v>
+        <v>7.215254151221195</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.46015972687929</v>
+        <v>9.473138869277754</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11.0493980862752</v>
+        <v>11.06250889065014</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>13.47449959845883</v>
+        <v>13.4875424947532</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.134446732250382</v>
+        <v>9.147512986550858</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.539603759000855</v>
+        <v>6.552784768296092</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.350944298350413</v>
+        <v>4.364143037305176</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.628478687790626</v>
+        <v>5.641883815443457</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>13.93436366134539</v>
+        <v>13.9478209550556</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>13.96874681869082</v>
+        <v>13.98219910741093</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>15.67615178221401</v>
+        <v>15.68970782856562</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>18.05353268895844</v>
+        <v>18.04310305326029</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>35</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-6.77915260592426</v>
+        <v>-6.766630316248637</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.676440504602809</v>
+        <v>-2.663530695026758</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.071309211199235</v>
+        <v>-3.058302079781633</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.630372492836599</v>
+        <v>5.643351635235064</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.949094134907362</v>
+        <v>7.962204939282302</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>11.10367892976596</v>
+        <v>11.11672182606033</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.794952358184396</v>
+        <v>-3.781753619229633</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.645077543212416</v>
+        <v>-4.631672415559585</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.849830867529995</v>
+        <v>-4.836373573819778</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.8988380041010728</v>
+        <v>0.9122902928211829</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.442590439718174</v>
+        <v>6.432160804020022</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>25</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>11.50656167979008</v>
+        <v>11.5190839694657</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.894988066825711</v>
+        <v>5.907897876401762</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>9.500119360229121</v>
+        <v>9.513126491646723</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.630372492836621</v>
+        <v>9.643351635235085</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9.091951277764451</v>
+        <v>9.105062082139391</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.389393215480226</v>
+        <v>5.402436111774591</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.304659498207947</v>
+        <v>9.317725752508423</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.837476099426389</v>
+        <v>8.850657108721627</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>12.77647621324409</v>
+        <v>12.78967495219885</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>23.92635102821622</v>
+        <v>23.93975615586905</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>27.72159770389858</v>
+        <v>27.7350549976088</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>19.75598086124413</v>
+        <v>19.76943314996424</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>23.33572625029911</v>
+        <v>23.34928229665071</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>19.58544758257551</v>
+        <v>19.57501794687736</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>32</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-11.86843832021002</v>
+        <v>-11.8559160305344</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-7.23001193317419</v>
+        <v>-7.217102123598139</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-4.499880639770865</v>
+        <v>-4.486873508353263</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.24462750716328</v>
+        <v>-1.231648364764816</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.591951277764551</v>
+        <v>7.60506208213949</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.485606784519874</v>
+        <v>-1.472563888225508</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.679659498207933</v>
+        <v>4.692725752508409</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.212476099426389</v>
+        <v>4.225657108721627</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>13.52647621324405</v>
+        <v>13.53967495219881</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>18.92635102821612</v>
+        <v>18.93975615586895</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>24.97159770389862</v>
+        <v>24.98505499760884</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>21.88098086124405</v>
+        <v>21.89443314996416</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.08572625029911</v>
+        <v>12.09928229665071</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.085447582575355</v>
+        <v>6.075017946877203</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>10</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-24.10501193317423</v>
+        <v>-24.09210212359818</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-4.49988063977068</v>
+        <v>-4.486873508353078</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-4.36962750716318</v>
+        <v>-4.356648364764716</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-15.16252390057361</v>
+        <v>-15.14934289127837</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-15.22352378675577</v>
+        <v>-15.21032504780101</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.721597703898432</v>
+        <v>3.73505499760865</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.755980861243863</v>
+        <v>3.769433149963973</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.585447582575682</v>
+        <v>3.57501794687753</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>20</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-7.493438320209904</v>
+        <v>-7.480916030534281</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-14.10501193317423</v>
+        <v>-14.09210212359818</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-9.499880639770893</v>
+        <v>-9.486873508353291</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-24.3696275071634</v>
+        <v>-24.35664836476493</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-24.90804872223549</v>
+        <v>-24.89493791786055</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-34.6106067845199</v>
+        <v>-34.59756388822554</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-24.69534050179211</v>
+        <v>-24.68227424749163</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-35.16252390057361</v>
+        <v>-35.14934289127837</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-30.22352378675591</v>
+        <v>-30.21032504780115</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-36.07364897178391</v>
+        <v>-36.06024384413108</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-36.27840229610142</v>
+        <v>-36.2649450023912</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-26.24401913875599</v>
+        <v>-26.23056685003588</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-26.66427374970089</v>
+        <v>-26.65071770334929</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-16.41455241742467</v>
+        <v>-16.42498205312283</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>12</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-10.8267716535433</v>
+        <v>-10.81424936386768</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-21.16654730643761</v>
+        <v>-21.15354017502001</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-21.03629417382999</v>
+        <v>-21.02331503143153</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-13.24138205556882</v>
+        <v>-13.22827125119388</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-21.27727345118637</v>
+        <v>-21.26423055489201</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-29.69534050179211</v>
+        <v>-29.68227424749163</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-13.49585723390707</v>
+        <v>-13.48267622461183</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.073648971783719</v>
+        <v>-6.060243844130888</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-14.57735247208932</v>
+        <v>-14.56390018336921</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-14.99760708303422</v>
+        <v>-14.98405103668262</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-14.74788575075806</v>
+        <v>-14.75831538645621</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>17</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.4477381503781714</v>
+        <v>0.4602604400537942</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.163835462585915</v>
+        <v>-1.150925653009864</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.558704169182583</v>
+        <v>-1.545697037764981</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>4.466881046999852</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.915480689529126</v>
+        <v>3.928591493904065</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.09527556842134</v>
+        <v>10.10831846471571</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.01054185114906</v>
+        <v>10.02360810544954</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.221347429985371</v>
+        <v>-2.208166420690134</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.282347316167673</v>
+        <v>-2.26914857721291</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.132472501195601</v>
+        <v>-3.119067373542769</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.33722582551318</v>
+        <v>-3.323768531802962</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.185195609344227</v>
+        <v>-9.171743320624117</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.605450220289129</v>
+        <v>-9.591894173937526</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-15.23808182918923</v>
+        <v>-15.24851146488738</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>40</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.006561679790018</v>
+        <v>5.01908396946564</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.89498806682574</v>
+        <v>10.90789787640179</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.50011936022921</v>
+        <v>10.51312649164681</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>20.63037249283668</v>
+        <v>20.64335163523514</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>20.09195127776454</v>
+        <v>20.10506208213948</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>25.38939321548017</v>
+        <v>25.40243611177453</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>25.30465949820789</v>
+        <v>25.31772575250837</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>27.33747609942643</v>
+        <v>27.35065710872167</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>22.27647621324409</v>
+        <v>22.28967495219885</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>16.42635102821616</v>
+        <v>16.43975615586899</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.22159770389858</v>
+        <v>16.2350549976088</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.25598086124401</v>
+        <v>16.26943314996412</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>15.83572625029911</v>
+        <v>15.84928229665071</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.58544758257537</v>
+        <v>18.57501794687722</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-21 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-21 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2663213353837364</v>
+        <v>-0.2665778851954741</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1270437569196474</v>
+        <v>-0.1273444143470854</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2393517465289037</v>
+        <v>-0.2396274863213961</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2427600077756153</v>
+        <v>-0.2430342609450733</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3024632249302499</v>
+        <v>-0.3027263087495982</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3346940180410272</v>
+        <v>-0.3349475236982684</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.283575795909762</v>
+        <v>-0.283842490569306</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.3451667051825851</v>
+        <v>-0.345421322650914</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2701152531610163</v>
+        <v>-0.2703887889141683</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2973428643519043</v>
+        <v>-0.2976151045527828</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2921412558658858</v>
+        <v>-0.2924161821802613</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.3421786479584412</v>
+        <v>-0.34244123668946</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.306885433549688</v>
+        <v>-0.3071594211407032</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3133984768402627</v>
+        <v>-0.3130527453171581</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3967</v>
+        <v>3968</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3828855563908817</v>
+        <v>-0.3834530815265609</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.4231823277457352</v>
+        <v>-0.4237604150554688</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.5531737518874635</v>
+        <v>-0.5537244759330164</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.5853680150838656</v>
+        <v>-0.5859092999081454</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7078475149920322</v>
+        <v>-0.7083651242975577</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.7238143316896384</v>
+        <v>-0.724324451605753</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.7949882119078637</v>
+        <v>-0.7954817946614412</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.8710564955899684</v>
+        <v>-0.8715371539859689</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.8428591341879326</v>
+        <v>-0.8433479524072425</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.8482649375355322</v>
+        <v>-0.8487634815932381</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.8124073338847921</v>
+        <v>-0.8129178052116472</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.8396351629434449</v>
+        <v>-0.8401386384489697</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.8427011690557293</v>
+        <v>-0.84320951488872</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.8561959767893654</v>
+        <v>-0.8554256015098574</v>
       </c>
     </row>
     <row r="8">
@@ -2318,101 +2318,101 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3770</v>
+        <v>3771</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3390634854227628</v>
+        <v>-0.3403240643609848</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.3768257882773511</v>
+        <v>-0.3781185127073527</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.5194521816909443</v>
+        <v>-0.5207180350586711</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.7188338563696703</v>
+        <v>-0.7200442917682963</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.8196655520846576</v>
+        <v>-0.8208638437864764</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.9314114430693294</v>
+        <v>-0.9325731499349104</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.134313231471751</v>
+        <v>-1.135424062208408</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.243032375149888</v>
+        <v>-1.244127111559024</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.236768819868495</v>
+        <v>-1.237867420682505</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.410161955355647</v>
+        <v>-1.411237221614449</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.335386128595452</v>
+        <v>-1.336487132756858</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.233414684885361</v>
+        <v>-1.234542466256393</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.241309018860257</v>
+        <v>-1.242446229330199</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.374764619016112</v>
+        <v>-1.373271631483931</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 25.95</t>
+          <t>X &gt; 25.96</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5069632568118365</v>
+        <v>-0.5090850446188639</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2154967133320653</v>
+        <v>-0.2177713261904586</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3414368844846649</v>
+        <v>-0.3436942524343962</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5625209081785556</v>
+        <v>-0.5647115167242589</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.6344238985401489</v>
+        <v>-0.636618684922027</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.7449182969351824</v>
+        <v>-0.7470702351930285</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.9273472757125205</v>
+        <v>-0.9294525770627402</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.8993957244019484</v>
+        <v>-0.901530303076278</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.9733119821809382</v>
+        <v>-0.9754295085577809</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.158394734495701</v>
+        <v>-1.16049800962098</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.065065195225458</v>
+        <v>-1.067204889396848</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.9585471206666654</v>
+        <v>-0.9607166098550408</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9108103626497197</v>
+        <v>-0.9130127853165035</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.154371421949484</v>
+        <v>-1.152151971132369</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3340709236163022</v>
+        <v>-0.337407365286559</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.01728803640289556</v>
+        <v>0.01373729246022037</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.004075537952857644</v>
+        <v>0.0005009972750045222</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1230521646975689</v>
+        <v>-0.1265814140649155</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2490962252805531</v>
+        <v>-0.2526243714374132</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3614444330120676</v>
+        <v>-0.3649207700768642</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.5210565286050368</v>
+        <v>-0.5244917315001629</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6059862596104892</v>
+        <v>-0.6094282051114064</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.7113286648046895</v>
+        <v>-0.7147444321351983</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7519045375050979</v>
+        <v>-0.7553657953505137</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.6347171222149015</v>
+        <v>-0.6382295403600935</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.6138696117495783</v>
+        <v>-0.617388082494692</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.7118927973199334</v>
+        <v>-0.7154110204075792</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.9336363868902495</v>
+        <v>-0.9304765586172579</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3395415757180302</v>
+        <v>-0.3441638937822091</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1576435121216022</v>
+        <v>-0.1624737118915078</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2715160461545025</v>
+        <v>-0.2763471925637475</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4854932082824774</v>
+        <v>-0.4902449425865143</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5451906386003245</v>
+        <v>-0.5499741258921489</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.8227279966410492</v>
+        <v>-0.8273959593482871</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.153330617113369</v>
+        <v>-1.157900070943548</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.372148158978355</v>
+        <v>-1.376690502481011</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.283530380887129</v>
+        <v>-1.288110149976497</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.291327072047686</v>
+        <v>-1.29598403536081</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.9171353874904042</v>
+        <v>-0.9219370868239238</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.029497686610775</v>
+        <v>-1.034262000151351</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.167410098330805</v>
+        <v>-1.172169848563811</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.394737357979423</v>
+        <v>-1.390317147213217</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2771</v>
+        <v>2772</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.7693003891754913</v>
+        <v>-0.7567780994998685</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.3141387747121414</v>
+        <v>-0.3205503994602452</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1145463478944677</v>
+        <v>-0.1210811978968778</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3962366405685742</v>
+        <v>-0.4026584294665199</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5555307366239788</v>
+        <v>-0.5619641674110767</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.7423088356173437</v>
+        <v>-0.748643024916106</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.9516399978324301</v>
+        <v>-0.9579129664552823</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.255429914257441</v>
+        <v>-1.261653906397164</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.333033873211242</v>
+        <v>-1.339241144308168</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.370946269081138</v>
+        <v>-1.37724672597539</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.051293428040857</v>
+        <v>-1.057737795183989</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.105180336015266</v>
+        <v>-1.111605062004152</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.180868266295413</v>
+        <v>-1.187320660435475</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.416356820167294</v>
+        <v>-1.410552038692735</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>2471</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4369867073067581</v>
+        <v>-0.4244644176311354</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2929909569741511</v>
+        <v>-0.3017795429530139</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3836578794802676</v>
+        <v>-0.3924806079901657</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5545285971915845</v>
+        <v>-0.5632666052814059</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5461747319285521</v>
+        <v>-0.5550105864112211</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6308088047218448</v>
+        <v>-0.6395671192432388</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.8554051743871014</v>
+        <v>-0.8640924293098138</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.179507321519836</v>
+        <v>-1.188146448271098</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.8141386734873066</v>
+        <v>-0.8229413033611976</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.07567244406227</v>
+        <v>-1.0845156887912</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.9162007582624909</v>
+        <v>-0.9027434645522732</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.124634274328628</v>
+        <v>-1.111181985608518</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.383011102999141</v>
+        <v>-1.369455056647539</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.699862008683205</v>
+        <v>-1.710291644381357</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>2151</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.09920308078645235</v>
+        <v>-0.0866807911108296</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1488234922093099</v>
+        <v>0.161733301785361</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.06008519579128091</v>
+        <v>-0.04707806437367879</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.02281207248178418</v>
+        <v>-0.00983293008331998</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.04313677288305939</v>
+        <v>0.05624757725799867</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3567713591362889</v>
+        <v>-0.3437284628419235</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5344850857065708</v>
+        <v>-0.5214188314060948</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6297484472960591</v>
+        <v>-0.6165674380008213</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5977683241803717</v>
+        <v>-0.5845695852256085</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2856433929832818</v>
+        <v>-0.2722382653304507</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.07198667545986126</v>
+        <v>-0.05852938174964351</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.45601355995543</v>
+        <v>-0.44256127123532</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7367981569533342</v>
+        <v>-0.7232421106017313</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.323896908359046</v>
+        <v>-1.334326544057198</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>1867</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9077400407969876</v>
+        <v>0.9202623304726103</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.7958986185129646</v>
+        <v>0.8088084280890158</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7759629595864297</v>
+        <v>0.7889700910040318</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.8526542282410645</v>
+        <v>0.8656333706395287</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.8498516526975521</v>
+        <v>0.8629624570724914</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5045512229788329</v>
+        <v>0.5175941192731983</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.205570049895087</v>
+        <v>0.218636304195563</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1668815627365134</v>
+        <v>0.1800625720317512</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.373690996318544</v>
+        <v>0.3868897352733072</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.023298001970851</v>
+        <v>1.036703129623682</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.407725181134786</v>
+        <v>1.421182474845004</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.174299018715892</v>
+        <v>1.187751307436002</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.5933588159123886</v>
+        <v>0.6069148622639915</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.228157130868631</v>
+        <v>-0.2385867665667831</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>1599</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7898637435799003</v>
+        <v>0.802386033255523</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8668454777075638</v>
+        <v>0.879755287283615</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9097503796162982</v>
+        <v>0.9227575110339004</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.29015985994112</v>
+        <v>1.303139002339584</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.126973166444934</v>
+        <v>1.140083970819873</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7364851479379482</v>
+        <v>0.7495280442323136</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3390559960190203</v>
+        <v>0.3521222503194963</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1845680318841687</v>
+        <v>0.1977490411794065</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7489590149951795</v>
+        <v>0.7621577539499427</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.337232829341865</v>
+        <v>1.350637956994696</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.945487635105586</v>
+        <v>1.958944928815804</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.667175357804361</v>
+        <v>1.680627646524471</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9342253122128099</v>
+        <v>0.9477813585644128</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3709385144077899</v>
+        <v>0.3605088787096378</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1394</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5194741618560244</v>
+        <v>0.5319964515316471</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7730368473135769</v>
+        <v>0.7859466568896281</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.378168140716987</v>
+        <v>0.3911752721345891</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9388373421910572</v>
+        <v>0.9518164845895214</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.9743042189409792</v>
+        <v>0.9874150233159185</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.913066099267823</v>
+        <v>0.9261089955621884</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3261803016512133</v>
+        <v>0.3392465559516893</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.06926708565251971</v>
+        <v>-0.05608607635728191</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.156677074076228</v>
+        <v>0.1698758130309912</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6695361071257651</v>
+        <v>0.6829412347785961</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.038670874630284</v>
+        <v>1.052128168340502</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7143739745869127</v>
+        <v>0.7278262633070227</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.3658553751197715</v>
+        <v>0.3794114214713744</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1735194188593283</v>
+        <v>-0.1839490545574805</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1176</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.05758208795328557</v>
+        <v>0.07010437762890831</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.02337928011300505</v>
+        <v>-0.01046947053695391</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.2481799594987137</v>
+        <v>-0.2351728280811116</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7324133091631992</v>
+        <v>0.7453924515616634</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.129366243750908</v>
+        <v>1.142477048125848</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.341774167861125</v>
+        <v>1.35481706415549</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.001938409772521</v>
+        <v>1.015004664072997</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.2796529701746806</v>
+        <v>0.2928339794699184</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.409129274468576</v>
+        <v>1.422328013423339</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.324310211889639</v>
+        <v>1.33771533954247</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.969897023626473</v>
+        <v>1.983354317336691</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.068906031312039</v>
+        <v>1.082358320032149</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.6486514203671376</v>
+        <v>0.6622074667187405</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.3031346574053373</v>
+        <v>0.2927050217071852</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1036</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2092643824927194</v>
+        <v>0.2217866721683421</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4316676035053035</v>
+        <v>0.4445774130813547</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5194243795342004</v>
+        <v>0.5324315109518025</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.228828091292279</v>
+        <v>1.241807233690743</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.366082551895786</v>
+        <v>1.379193356270726</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.760049586136539</v>
+        <v>1.773092482430904</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.578790772339168</v>
+        <v>1.591857026639644</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6289818909321809</v>
+        <v>0.6421629002274187</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.436707873475754</v>
+        <v>1.449906612430517</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.6831077849729184</v>
+        <v>0.6965129126257494</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.05750503980591</v>
+        <v>1.070962333516128</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1629380576749</v>
+        <v>-0.1494857689547899</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.1005671859943291</v>
+        <v>-0.08701113964272622</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3334713363435142</v>
+        <v>-0.3439009720416664</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>891</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.0804192405242361</v>
+        <v>-0.06789695084861336</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5696583978206959</v>
+        <v>-0.5567485882446448</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6067411335176232</v>
+        <v>0.6197482649352253</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.634861830659347</v>
+        <v>1.647840973057811</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.657607843421069</v>
+        <v>1.670718647796008</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.291750117837069</v>
+        <v>2.304793014131434</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.09478295499801</v>
+        <v>2.107849209298486</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2807982094151669</v>
+        <v>0.2939792187104047</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.454366224467428</v>
+        <v>1.467564963422191</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1553072571723888</v>
+        <v>0.1687123848252199</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.072888388522607</v>
+        <v>1.086345682232825</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5762301376336509</v>
+        <v>-0.5627778489135409</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3230840751778814</v>
+        <v>-0.3095280288262785</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1855961884683737</v>
+        <v>-0.1960258241665258</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>799</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.303200522963408</v>
+        <v>-0.2906782332877853</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2877403436873749</v>
+        <v>-0.2748305341113237</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8192682963993931</v>
+        <v>0.8322754278169953</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.075929439019404</v>
+        <v>2.088908581417869</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.163290451731967</v>
+        <v>2.176401256106907</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.335575943890682</v>
+        <v>2.348618840185047</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.250842226618403</v>
+        <v>2.263908480918879</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.2817814811535442</v>
+        <v>0.294962490448782</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.597502496097661</v>
+        <v>1.610701235052424</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8725337566266731</v>
+        <v>0.8859388842795042</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.794188442321605</v>
+        <v>1.807645736031823</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2015378074267389</v>
+        <v>0.2149900961468489</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.5322218698235091</v>
+        <v>0.545777916175112</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.032256093213704</v>
+        <v>1.021826457515552</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>696</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.344013032853653</v>
+        <v>-1.33149074317803</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.6567360711052714</v>
+        <v>-0.6438262615292203</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6725331533326226</v>
+        <v>0.6855402847502248</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.239567895135529</v>
+        <v>2.252547037533994</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.70114668006336</v>
+        <v>1.714257484438299</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.711232295939936</v>
+        <v>1.724275192234302</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.913854900506742</v>
+        <v>1.926921154807218</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4211445902287849</v>
+        <v>-0.4079635809335471</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8109589718647712</v>
+        <v>0.8241577108195344</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.5355464305150122</v>
+        <v>0.5489515581678432</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.767574715392833</v>
+        <v>1.78103200910305</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2214981026233289</v>
+        <v>0.234950391343439</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.08859981351749724</v>
+        <v>0.1021558598691001</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6256774676328689</v>
+        <v>0.6152478319347168</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>597</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.739669475988869</v>
+        <v>-1.727147186313246</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.8386802748827762</v>
+        <v>-0.825770465306725</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3960280434559138</v>
+        <v>-0.3830209120383117</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.911779528012559</v>
+        <v>1.924758670411023</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.043375063359143</v>
+        <v>2.056485867734082</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.508321188679496</v>
+        <v>2.521364084973861</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.423587471407217</v>
+        <v>2.436653725707693</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5561587414446336</v>
+        <v>-0.5429777321493958</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.057883248419969</v>
+        <v>1.071081987374733</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.882799939438939</v>
+        <v>1.896205067091771</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.018080115958881</v>
+        <v>3.031537409669099</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.377421397257415</v>
+        <v>1.390873685977525</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.292175161521889</v>
+        <v>1.305731207873492</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.541896493798177</v>
+        <v>1.531466858100025</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>501</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.393637921008377</v>
+        <v>-2.381115631332754</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.21080035632793</v>
+        <v>-1.197890546751879</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.006866667714931</v>
+        <v>-0.9938595362973288</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.119394448924503</v>
+        <v>1.132373591322967</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.177779621077882</v>
+        <v>2.190890425452821</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.876419163583968</v>
+        <v>1.889462059878333</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.592084647908486</v>
+        <v>1.605150902208962</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.070707533308145</v>
+        <v>-1.057526524012907</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4650989677351021</v>
+        <v>0.4782977066898653</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.411380968335919</v>
+        <v>1.42478609598875</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.202635628050274</v>
+        <v>3.216092921760492</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.640212398170156</v>
+        <v>1.653664686890266</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8207561904188694</v>
+        <v>0.8343122367704723</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.270078321098353</v>
+        <v>1.259648685400201</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>397</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.35238038570116</v>
+        <v>-0.3398580960255373</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.05115935146052664</v>
+        <v>0.06406916103657778</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6638473199269086</v>
+        <v>0.6768544513445107</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.557324633894609</v>
+        <v>2.570303776293073</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.278349262651162</v>
+        <v>3.291460067026101</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.568234525303851</v>
+        <v>2.581277421598216</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.735389976797308</v>
+        <v>2.748456231097784</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.2530932278898703</v>
+        <v>0.2662742371851081</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.703428354302019</v>
+        <v>1.716627093256783</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.868416519400043</v>
+        <v>2.881821647052874</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.938222389037122</v>
+        <v>5.95167968274734</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.705603027490866</v>
+        <v>3.719055316210977</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.522124235185764</v>
+        <v>1.535680281537367</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.519956398696308</v>
+        <v>1.509526762998156</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>322</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.251202295365253</v>
+        <v>-1.238680005689631</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3783038586400735</v>
+        <v>-0.3653940490640224</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.7796224658192443</v>
+        <v>0.7926295972368465</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.083788641905002</v>
+        <v>3.096767784303466</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.166485439255197</v>
+        <v>3.179596243630137</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.842809364548494</v>
+        <v>2.855852260842859</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1935798011947298</v>
+        <v>-0.180398791899492</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.298215343678869</v>
+        <v>1.311414082633632</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.622003202129207</v>
+        <v>2.635408329782038</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.143957952345787</v>
+        <v>6.157415246056004</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.867782103480032</v>
+        <v>5.881234392200142</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.894732461479229</v>
+        <v>3.908288507830832</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.45501279996671</v>
+        <v>4.444583164268558</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>275</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.675256502028155</v>
+        <v>-2.662734212352532</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.105011933174232</v>
+        <v>-2.092102123598181</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3180624579526352</v>
+        <v>-0.3050553265350331</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.994008856473037</v>
+        <v>2.006987998871502</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.819224005037235</v>
+        <v>1.832334809412174</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.025756851843809</v>
+        <v>1.038799748138175</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.304659498207897</v>
+        <v>1.317725752508373</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.34434208239179</v>
+        <v>-1.331161073096553</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.776476213244095</v>
+        <v>0.7896749521988582</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.10816921003434</v>
+        <v>2.121574337687171</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.812506794807675</v>
+        <v>4.825964088517892</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.483253588516739</v>
+        <v>4.496705877236849</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.881180795753657</v>
+        <v>1.89473684210526</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.130902128029945</v>
+        <v>2.120472492331793</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>240</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.076771653543311</v>
+        <v>-2.064249363867688</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.021678599840897</v>
+        <v>-2.008768790264845</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.0834526935625064</v>
+        <v>0.09645982498010852</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.463705826170013</v>
+        <v>1.476684968568478</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.9252846110978439</v>
+        <v>0.9383954154727832</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4439401178531668</v>
+        <v>-0.4308972215588014</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7213261648745615</v>
+        <v>0.7343924191750375</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.829190567240275</v>
+        <v>-1.816009557945037</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.443142879910752</v>
+        <v>1.456341618865515</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.093017694882825</v>
+        <v>3.106422822535656</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.221597703898581</v>
+        <v>6.235054997608799</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.005980861244019</v>
+        <v>5.019433149964129</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.085726250299111</v>
+        <v>2.099282296650713</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.502114249242069</v>
+        <v>1.491684613543917</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>215</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.656229017884399</v>
+        <v>-3.643706728208777</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.942221235499808</v>
+        <v>-2.929311425923757</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.011508546747571</v>
+        <v>-0.9985014153299687</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.5140934230692409</v>
+        <v>0.5270725654677051</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.02432779200292856</v>
+        <v>-0.01121698762798928</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.12223469149658</v>
+        <v>-1.109191795202214</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2767358506293149</v>
+        <v>-0.2636695963288389</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.069500644759657</v>
+        <v>-3.056319635464419</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1253134225464123</v>
+        <v>0.1385121615011755</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.6705370747277826</v>
+        <v>0.6839422023806137</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>3.735054997608799</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.290864582174244</v>
+        <v>3.304316870894354</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.3852039822590285</v>
+        <v>-0.3716479359074256</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.6005989290525093</v>
+        <v>-0.6110285647506615</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>183</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.220214276494126</v>
+        <v>-2.207691986818503</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.1924436271633</v>
+        <v>-2.179533817587249</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.401519984033115</v>
+        <v>-0.3885128526155128</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.8216293234377687</v>
+        <v>0.8346084658362329</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.356136153929477</v>
+        <v>-1.343025349554537</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.058694216213816</v>
+        <v>-1.04565131991945</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.143427933486095</v>
+        <v>-1.130361679185619</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.342851769426069</v>
+        <v>-4.329670760130831</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.218059305881589</v>
+        <v>-2.204860566926826</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.521736403477824</v>
+        <v>-2.508331275824993</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.005750709363056217</v>
+        <v>0.01920800307327397</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.04013386670848718</v>
+        <v>0.05358615542859724</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.565913093963182</v>
+        <v>-2.552357047611579</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.769743674255196</v>
+        <v>-1.780173309953348</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>173</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.204420979169512</v>
+        <v>-2.19189868949389</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.9258211817291482</v>
+        <v>-0.912911372153097</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1646205241638938</v>
+        <v>-0.1516133927462917</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.121701972605457</v>
+        <v>1.134681115003922</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.150823288709482</v>
+        <v>-1.137712484334543</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.8533813509938213</v>
+        <v>-0.8403384546994559</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9381150682661001</v>
+        <v>-0.9250488139656241</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-3.717437195371296</v>
+        <v>-3.704256186076059</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.466298353229902</v>
+        <v>-1.453099614275139</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.31642353825783</v>
+        <v>-2.303018410604999</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2090381342517063</v>
+        <v>-0.1955808405414885</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1746549769062753</v>
+        <v>-0.1612026881861652</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.90704831617488</v>
+        <v>-2.893492269823277</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.079292301817674</v>
+        <v>-2.089721937515826</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>153</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.513046163347234</v>
+        <v>-1.500523873671611</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.7969488511394971</v>
+        <v>0.8098586607155482</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>4.466881046999852</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.954696375803721</v>
+        <v>1.96780718017866</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.559327856003051</v>
+        <v>3.572370752297417</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.167404596247103</v>
+        <v>2.180470850547579</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>0.4062126642771844</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.292816082525128</v>
+        <v>2.306014821479891</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.096285668739043</v>
+        <v>2.109690796391874</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.505911429388775</v>
+        <v>4.519368723098992</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.23310504425055</v>
+        <v>3.24655733297066</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1984713483383231</v>
+        <v>0.212027394689926</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2054020906272171</v>
+        <v>-0.2158317263253693</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>141</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.7203886748199082</v>
+        <v>-0.7078663851442855</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.214137002995983</v>
+        <v>1.227046812572034</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.946927870867484</v>
+        <v>2.959935002285086</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.623280294255117</v>
+        <v>6.636259436653582</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.247979646558832</v>
+        <v>3.261090450933771</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.673081158742576</v>
+        <v>5.686124055036942</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.879127583314272</v>
+        <v>4.892193837614748</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.575064751908663</v>
+        <v>1.5882457612039</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.932504582038412</v>
+        <v>2.945703320993175</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.79159925516651</v>
+        <v>2.805004382819341</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.423725363473046</v>
+        <v>5.437182657183264</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.748888662662452</v>
+        <v>4.762340951382562</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.491754619093435</v>
+        <v>1.505310665445037</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.032256093213704</v>
+        <v>1.021826457515552</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>124</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.8805350944035268</v>
+        <v>-0.8680128047279041</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.540149357148344</v>
+        <v>1.553059166724395</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.564635489261441</v>
+        <v>3.577642620679043</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.920695073481838</v>
+        <v>6.933674215880302</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.156467406796772</v>
+        <v>3.169578211171711</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.066812570318881</v>
+        <v>5.079855466613246</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.175627240143378</v>
+        <v>4.188693494443854</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.095540615555429</v>
+        <v>2.108721624850666</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3.647443955179575</v>
+        <v>3.660642694134339</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.603770383054872</v>
+        <v>3.617175510707703</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.624823510350197</v>
+        <v>6.638280804060415</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.659206667695628</v>
+        <v>6.672658956415738</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.013145605137822</v>
+        <v>3.026701651489425</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.26286693741411</v>
+        <v>3.252437301715958</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-3.683914510686165</v>
+        <v>-3.671392221010542</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-2.914535742698042</v>
+        <v>-2.901625933121991</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3922772547414439</v>
+        <v>0.4052563971399081</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-5.8858166922683</v>
+        <v>-5.872750437967824</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-9.92442866247837</v>
+        <v>-9.911247653183132</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-2.50222040035527</v>
+        <v>-2.488815272702439</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.089314194577348</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-3.09284517827232</v>
+        <v>-3.079289131920717</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.033600036472215</v>
+        <v>-4.044029672170367</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Realized VOL-21 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Realized VOL-21 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.98275215598051</v>
+        <v>12.99527444565613</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8.990226162063863</v>
+        <v>9.003135971639914</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.97630983641966</v>
+        <v>10.98931696783726</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.33004651585973</v>
+        <v>15.34315732023467</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>18.00844083452779</v>
+        <v>18.02148373082215</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.73323092677932</v>
+        <v>16.7462971810798</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>18.6469999089502</v>
+        <v>18.66018091824544</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>17.39552383229171</v>
+        <v>17.40872257124647</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>18.92635102821616</v>
+        <v>18.93975615586899</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>17.53112151342239</v>
+        <v>17.54457880713261</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>19.9464570517202</v>
+        <v>19.95990934044031</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>18.33572625029911</v>
+        <v>18.34928229665071</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>18.5854475825754</v>
+        <v>18.57501794687725</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>190</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8.03287746926371</v>
+        <v>8.045399758939332</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10.10551438261525</v>
+        <v>10.1184241921913</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>11.28959304443971</v>
+        <v>11.30260017585731</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.47247775599457</v>
+        <v>12.48545689839303</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>15.09195127776451</v>
+        <v>15.10506208213945</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>15.91570900495385</v>
+        <v>15.92875190124822</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17.93623844557631</v>
+        <v>17.94930469987679</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>19.04800241521585</v>
+        <v>19.06118342451109</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>19.51331831850724</v>
+        <v>19.526517057462</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>19.71582471242669</v>
+        <v>19.72922984007953</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>18.45843980916173</v>
+        <v>18.47189710287195</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>19.01913875598086</v>
+        <v>19.03259104470097</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>19.12519993450965</v>
+        <v>19.13875598086125</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>19.37492126678593</v>
+        <v>19.36449163108778</v>
       </c>
     </row>
     <row r="8">
@@ -4015,98 +4015,98 @@
         <v>387</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.320515168162117</v>
+        <v>3.33303745783774</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.292920883363237</v>
+        <v>4.305830692939288</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.931643908032797</v>
+        <v>4.944651039450399</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.129080503172588</v>
+        <v>7.142059645571052</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.141046884999646</v>
+        <v>8.154157689374586</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.472080553981456</v>
+        <v>9.485123450275822</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.71292823205801</v>
+        <v>11.72599448635849</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>12.53773449735922</v>
+        <v>12.55091550665446</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>12.99353047680997</v>
+        <v>13.00672921576474</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>14.72738461994743</v>
+        <v>14.74078974760026</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>13.74743749718023</v>
+        <v>13.76089479089045</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>12.74822892325952</v>
+        <v>12.76168121197963</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>12.84477017794769</v>
+        <v>12.85832622429929</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>14.12808324149013</v>
+        <v>14.11765360579198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 25.95</t>
+          <t>X &lt; 25.96</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>621</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.90108663953238</v>
+        <v>2.913608929208003</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.611574218194534</v>
+        <v>1.624484027770585</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.86082789485075</v>
+        <v>1.873835026268353</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.279325793963892</v>
+        <v>3.292304936362356</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.707088153770954</v>
+        <v>3.720198958145893</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.48762187892622</v>
+        <v>4.500664775220585</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.691132928159583</v>
+        <v>5.704199182460059</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.384980125191284</v>
+        <v>5.398161134486521</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6.129133218074998</v>
+        <v>6.142331957029761</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.211375182805533</v>
+        <v>7.224780310458364</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>6.523530071048341</v>
+        <v>6.536987364758559</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.913790845140952</v>
+        <v>5.927243133861062</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.654566830009252</v>
+        <v>5.668122876360854</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.031502332977979</v>
+        <v>7.021072697279827</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>882</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.248058278429482</v>
+        <v>1.260580568105105</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2033780895015056</v>
+        <v>0.2162878990775567</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.07811193228782543</v>
+        <v>-0.0651048008702233</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5056559395486957</v>
+        <v>0.5186350819471599</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.9876428877418348</v>
+        <v>1.000753692116774</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.511842195071999</v>
+        <v>1.524885091366365</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.220759271450525</v>
+        <v>2.233825525751001</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.433847981512564</v>
+        <v>2.447028990807802</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.053120204173801</v>
+        <v>3.066318943128564</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.223403182411168</v>
+        <v>3.236808310063999</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.678513803671819</v>
+        <v>2.691971097382037</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.599518276209999</v>
+        <v>2.612970564930109</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.972914458915888</v>
+        <v>2.986470505267491</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.789529215228463</v>
+        <v>3.77909957953031</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>1129</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.9166591111452078</v>
+        <v>0.9291814008208306</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.6336948870206314</v>
+        <v>0.6466046965966825</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.681695976703935</v>
+        <v>0.6947031081215371</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.343392864847303</v>
+        <v>1.356372007245767</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.513563323822964</v>
+        <v>1.526674128197904</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.3424490170745</v>
+        <v>2.355491913368866</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.320602810873964</v>
+        <v>3.333669065174441</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.827732963908225</v>
+        <v>3.840913973203463</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.766733077725924</v>
+        <v>3.779931816680687</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.802347485257783</v>
+        <v>3.815752612910615</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.711854568380417</v>
+        <v>2.725311862090635</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.011959603493793</v>
+        <v>3.025411892213903</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.388870625852704</v>
+        <v>3.402426672204307</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.992887795152896</v>
+        <v>3.982458159454744</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>1386</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.546965720194066</v>
+        <v>1.520525930532699</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8011929730306733</v>
+        <v>0.8141027826067244</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1898740499838638</v>
+        <v>0.2028811814014659</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8251776876418759</v>
+        <v>0.8381568300403401</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.152557338370563</v>
+        <v>1.165668142745503</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.594299420386371</v>
+        <v>1.607342316680736</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.08676628031467</v>
+        <v>2.099832534615146</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.629683891634187</v>
+        <v>2.642864900929425</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.929434366202244</v>
+        <v>2.942633105157007</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.017260119125254</v>
+        <v>3.030665246778085</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.30745628975717</v>
+        <v>2.320913583467387</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.413989519252667</v>
+        <v>2.427441807972777</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.57093548550835</v>
+        <v>2.584491531859953</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.03710703423485</v>
+        <v>3.026677398536698</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6426563543462365</v>
+        <v>0.6237557613047997</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5695442798435195</v>
+        <v>0.5824540894195707</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5297051590457471</v>
+        <v>0.5427122904633492</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.8374730845526486</v>
+        <v>0.8504522269511128</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.8315962481787125</v>
+        <v>0.8447070525536517</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.010694990628096</v>
+        <v>1.023737886922461</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.399334054420912</v>
+        <v>1.412400308721388</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.819724620136448</v>
+        <v>1.832905629431686</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.403695148155329</v>
+        <v>1.416893887110092</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.796173513423263</v>
+        <v>1.809578641076094</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.507269699162045</v>
+        <v>1.486534287549631</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.812852899158713</v>
+        <v>1.791931669798345</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.197611253262956</v>
+        <v>2.176296514660187</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.660180678660808</v>
+        <v>2.67401024089029</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1068588566102378</v>
+        <v>0.09334139520822049</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.0415827954140795</v>
+        <v>-0.05545031577252502</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.03655961803780627</v>
+        <v>0.02254175428305416</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.04505503251921539</v>
+        <v>0.03105614688610814</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.01971125325286494</v>
+        <v>-0.03382680674943828</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.4539413783401542</v>
+        <v>0.4396569554469849</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6946247242386931</v>
+        <v>0.6801885131836372</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7519890218915961</v>
+        <v>0.7373933233266996</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.8182464767945632</v>
+        <v>0.8035914531928796</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.493515207320641</v>
+        <v>0.4787914616869884</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.217366743221632</v>
+        <v>0.2027166891510888</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.628490821403382</v>
+        <v>0.6136342450363017</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.9341318307674698</v>
+        <v>0.919003412188566</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.561519367221464</v>
+        <v>1.57202841025542</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7348625494761478</v>
+        <v>-0.7448049194232382</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5428920374314004</v>
+        <v>-0.5532397701461633</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.6537267936169755</v>
+        <v>-0.6641106934096968</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6739753332502758</v>
+        <v>-0.6843319805840622</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.667074385567382</v>
+        <v>-0.6775466135127246</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3460288906991238</v>
+        <v>-0.3565895515573558</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.05885813348562863</v>
+        <v>-0.06956754601208104</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.06670508524260299</v>
+        <v>-0.0775100658539003</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1472710634443644</v>
+        <v>-0.1580602394387753</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.6682435663784361</v>
+        <v>-0.6789802275732768</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.023278004780011</v>
+        <v>-1.033907513289194</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8338969747071161</v>
+        <v>-0.8446095888060441</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3569843564228421</v>
+        <v>-0.367995190260288</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.310338412269715</v>
+        <v>0.3187979556070601</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4903266904939159</v>
+        <v>-0.4980233400211347</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4474243845360988</v>
+        <v>-0.4553848929486293</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5878526133013864</v>
+        <v>-0.5958229246956321</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7870729900293725</v>
+        <v>-0.7949512063374584</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6813249201318641</v>
+        <v>-0.6893304412250458</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4017213597341751</v>
+        <v>-0.4097960658647324</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1144438156322707</v>
+        <v>-0.1226483706405048</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.05331953239888776</v>
+        <v>-0.06162359303275622</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3269182463735518</v>
+        <v>-0.3351300400008341</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.6872321099571437</v>
+        <v>-0.6954369771782183</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.104642046199039</v>
+        <v>-1.112720178035232</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.9315191387559878</v>
+        <v>-0.9396648586262728</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.4704480365316783</v>
+        <v>-0.4788427033492795</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1205727458061503</v>
+        <v>-0.1139230456979732</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2763</v>
+        <v>2764</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2600089253972939</v>
+        <v>-0.2662959369081364</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3032101313724382</v>
+        <v>-0.3096813743186431</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2100464652935301</v>
+        <v>-0.2166032380829463</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4568976117432015</v>
+        <v>-0.4633534837266495</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4708192850060513</v>
+        <v>-0.4773396488378339</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.406348394047086</v>
+        <v>-0.4128597035212849</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.07440187363326345</v>
+        <v>-0.08104725362660758</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.09208064980558106</v>
+        <v>0.08531414843281482</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.05104268723253114</v>
+        <v>0.0442795025780427</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2008625605080852</v>
+        <v>-0.2076426880616467</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.4215693243009895</v>
+        <v>-0.4282988151848386</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2584856848681056</v>
+        <v>-0.26527400838728</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.07961383653157128</v>
+        <v>-0.0865224049767761</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1905869238710949</v>
+        <v>0.1958573101189245</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2981</v>
+        <v>2982</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.02182843377043753</v>
+        <v>-0.02682588028392985</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.08810534046426</v>
+        <v>0.08291457646862455</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.0789963655767707</v>
+        <v>0.07376798847270294</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2740073132482408</v>
+        <v>-0.279108257812986</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.42644337106492</v>
+        <v>-0.4315477473490148</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4787901234291638</v>
+        <v>-0.4838515136435291</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3111370212030877</v>
+        <v>-0.3162655489302395</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.05706692032587313</v>
+        <v>-0.062328165709431</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4345083815315292</v>
+        <v>-0.4396521318319486</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3952570119848531</v>
+        <v>-0.4004983652294598</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6818875507931068</v>
+        <v>-0.6870555551550197</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3271569195136195</v>
+        <v>-0.3324435256390927</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1585728778028326</v>
+        <v>-0.1639594063328573</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.02407942178555089</v>
+        <v>-0.0198848029550831</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.06842236615764108</v>
+        <v>-0.07262256960931524</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.06734835194218647</v>
+        <v>-0.07168093661668706</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1895358121846158</v>
+        <v>-0.1938636136835754</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3932621286899902</v>
+        <v>-0.3975168194264143</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4352052717562529</v>
+        <v>-0.4394923733060949</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.5358225083932808</v>
+        <v>-0.5400559010050188</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4434223432243272</v>
+        <v>-0.4476945095561931</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1577269706087847</v>
+        <v>-0.1621306150635391</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3610797688416412</v>
+        <v>-0.3654257833304086</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1056489717838431</v>
+        <v>-0.1101478748411822</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2604765598658219</v>
+        <v>-0.2649450023911939</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.1440692378050059</v>
+        <v>0.1394715622560554</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1262451484413276</v>
+        <v>0.1216165905988333</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.201916662998336</v>
+        <v>0.2053830974217732</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.02257265874702341</v>
+        <v>0.0190839694656475</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2268977678629867</v>
+        <v>0.2232379190977696</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1819068832862314</v>
+        <v>-0.1854702136613327</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.431898569434388</v>
+        <v>-0.4353789109961639</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4347662794873983</v>
+        <v>-0.4382834612060975</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5788413599627091</v>
+        <v>-0.5822967126529406</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4943016994700784</v>
+        <v>-0.4977904356406881</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.02804957294524968</v>
+        <v>-0.03171380481335717</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2861957525156171</v>
+        <v>-0.289787150490632</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.07314001904185119</v>
+        <v>0.06938012407443495</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2062089648074448</v>
+        <v>-0.2098991308315732</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2431289640591885</v>
+        <v>0.2393016112672726</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1768649096195887</v>
+        <v>0.1730277066874351</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1378052065802962</v>
+        <v>0.1406745125338063</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3358</v>
+        <v>3359</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.07256583286032736</v>
+        <v>0.06949915333278511</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1383115089622748</v>
+        <v>0.1351301516910439</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2107740799607924</v>
+        <v>-0.2138764757122757</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.4800788135766254</v>
+        <v>-0.4830953816838317</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4975943117810786</v>
+        <v>-0.5006386304496218</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5107850376392591</v>
+        <v>-0.5138098044713786</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.460570813827772</v>
+        <v>-0.4636170876580081</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.01983662352247961</v>
+        <v>-0.02304274268995954</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2725871230627845</v>
+        <v>-0.2757233831162509</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.09506479569817117</v>
+        <v>-0.09830509896300299</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3426688834266116</v>
+        <v>-0.3458492260675854</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.0357427660059173</v>
+        <v>0.0324501092024434</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.04027851302330987</v>
+        <v>-0.04357484620643248</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.1608299635830335</v>
+        <v>-0.1582359977491379</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3461</v>
+        <v>3462</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.2699468265948539</v>
+        <v>0.2672854083145637</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1996238284151701</v>
+        <v>0.1969019063384891</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1508022987570001</v>
+        <v>-0.1534441965190751</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4370432375004043</v>
+        <v>-0.4395976735206162</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3259161573939906</v>
+        <v>-0.3285305424644136</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3010074763618604</v>
+        <v>-0.303615761424318</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3124108593468975</v>
+        <v>-0.3150214368833844</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1302364109348915</v>
+        <v>0.1274737177181677</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.05906908392844201</v>
+        <v>-0.06178163851358676</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.001387103252241673</v>
+        <v>-0.001386371540121445</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2737833584570737</v>
+        <v>-0.2764890139352119</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.03666235128155648</v>
+        <v>0.03386733010268728</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.06593999957697605</v>
+        <v>0.06311423427705165</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.04356137437346064</v>
+        <v>-0.04138875445146795</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3560</v>
+        <v>3561</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2913363789224093</v>
+        <v>0.289089565436548</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2062982571953142</v>
+        <v>0.204007588128654</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.05066542575703892</v>
+        <v>0.04840084774980369</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3080028573033786</v>
+        <v>-0.3101627864954679</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3269335639278452</v>
+        <v>-0.3291115873283417</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3785440042507702</v>
+        <v>-0.3806964183459485</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3359348387699654</v>
+        <v>-0.338103843904193</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.1375321846759689</v>
+        <v>0.1352099542500866</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.07625870961705772</v>
+        <v>-0.07852471128965277</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2094514409196364</v>
+        <v>-0.2117164949023902</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4265920238589231</v>
+        <v>-0.4288058329187052</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.1519360393736164</v>
+        <v>-0.1542266872517146</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1352088802821925</v>
+        <v>-0.1375228689865722</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1785973612448259</v>
+        <v>-0.1767371780876488</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3656</v>
+        <v>3657</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.3274938138865124</v>
+        <v>0.3256234790024379</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.2297754168802939</v>
+        <v>0.2278760720954693</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1224264232234447</v>
+        <v>0.120541976924855</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1415860450793005</v>
+        <v>-0.1433950241594673</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.283219254295517</v>
+        <v>-0.2850088398463697</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2165019810263829</v>
+        <v>-0.2183005867247871</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-0.1517065619021167</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1897426204531527</v>
+        <v>0.1878124458769719</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.03460240827276806</v>
+        <v>0.03271154422506584</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.0900424144067884</v>
+        <v>-0.09192917600754669</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3614851056122177</v>
+        <v>-0.3633056581289011</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1477916920638052</v>
+        <v>-0.1496704302490457</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.03315534663826725</v>
+        <v>-0.03508074326180832</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.09617167344210031</v>
+        <v>-0.09465664978668542</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3760</v>
+        <v>3761</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.03770400685072417</v>
+        <v>0.03630707492404639</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.05723621104633736</v>
+        <v>0.05579079980494583</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.08460617676366411</v>
+        <v>-0.0860251520435682</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2582216716195518</v>
+        <v>-0.2595918810735256</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3312378970829357</v>
+        <v>-0.3326037003539142</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2316258928000892</v>
+        <v>-0.2330109564133167</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.22228501997634</v>
+        <v>-0.2236755213769825</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.01538369369086467</v>
+        <v>0.01391699722707074</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.08408155568021414</v>
+        <v>-0.08552419809323908</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.2022355817732091</v>
+        <v>-0.203670138951729</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5515885836379582</v>
+        <v>-0.5529365007971521</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3163211057947919</v>
+        <v>-0.317731346448312</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.08357712646238724</v>
+        <v>-0.08506113769272616</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.08476518338205352</v>
+        <v>-0.08358348891110978</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3835</v>
+        <v>3836</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1053142785426218</v>
+        <v>0.1041710050593068</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.09306449001267225</v>
+        <v>0.09188956039350415</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.07970383269853443</v>
+        <v>-0.08084283510133616</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.247390836162019</v>
+        <v>-0.2484840381917977</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2514410219233127</v>
+        <v>-0.2525452000452049</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1999900788211519</v>
+        <v>-0.201101869494984</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1404211889342264</v>
+        <v>-0.141550854309223</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.05747089244903947</v>
+        <v>0.05627918055921555</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.01519045342257641</v>
+        <v>-0.01636514152674806</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1215781199995192</v>
+        <v>-0.1227438441310156</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.442029185106108</v>
+        <v>-0.4431164011929667</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.4191559644010212</v>
+        <v>-0.4202489761432204</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.2513436141430176</v>
+        <v>-0.2524899212278413</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2998196925223837</v>
+        <v>-0.2988089561467362</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3882</v>
+        <v>3883</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1894885090583216</v>
+        <v>0.1884884869194465</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2093178048843214</v>
+        <v>0.2082829855160639</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.008210806414638228</v>
+        <v>0.007219968791105202</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.130161936762498</v>
+        <v>-0.1311153568018497</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1149364117754601</v>
+        <v>-0.1159040021359914</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.03477130894142988</v>
+        <v>-0.0357545847045202</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.02833098777822585</v>
+        <v>-0.02931794929111931</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1358300088914177</v>
+        <v>0.1347918477290904</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.03760304627727606</v>
+        <v>0.03658853244576221</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.05203291414102296</v>
+        <v>-0.05304034528871426</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2681062858054091</v>
+        <v>-0.2690623467041249</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.245049004873394</v>
+        <v>-0.2460108654798958</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.05855652075419471</v>
+        <v>-0.05957455195896699</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.07761269563171425</v>
+        <v>-0.07679765961258767</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3917</v>
+        <v>3918</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1274268197391351</v>
+        <v>0.1265629824394452</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1836111261283904</v>
+        <v>0.1827070367071641</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.01922890860991799</v>
+        <v>-0.02008806676502672</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.07882027517961632</v>
+        <v>-0.07966262138400282</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.04304617511373721</v>
+        <v>-0.04390659624099413</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.06455245114896258</v>
+        <v>0.06366891870271019</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.01923646049127115</v>
+        <v>0.01836269518352651</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1522861937419577</v>
+        <v>0.1513706663159198</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.003401251489876245</v>
+        <v>0.002522262930433783</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.09303178229136222</v>
+        <v>-0.09390014193824925</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3090145409993781</v>
+        <v>-0.3098315109349343</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.23483312191496</v>
+        <v>-0.2356688908522031</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.05375818053294523</v>
+        <v>-0.0546472772201696</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.01935200894872935</v>
+        <v>-0.01865229304107885</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3942</v>
+        <v>3943</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1993556115220088</v>
+        <v>0.1985581858458332</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.2197225129562668</v>
+        <v>0.2188966121793143</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.04097440702907562</v>
+        <v>0.04018769549098522</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.01740078651554455</v>
+        <v>-0.01817125876941361</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.01475563109277545</v>
+        <v>0.01396896473053744</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.09825397497384358</v>
+        <v>0.09745003230098348</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.07801984259887718</v>
+        <v>0.07721942339443899</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2072835968934612</v>
+        <v>0.2064433837279651</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.08430494392561627</v>
+        <v>0.08349460772063111</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.05914372968600645</v>
+        <v>0.05832722250187317</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1313807498403321</v>
+        <v>-0.132152300921355</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1081165018391559</v>
+        <v>-0.1088938462335918</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.09453933678148729</v>
+        <v>0.09370420334442287</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1049808144373969</v>
+        <v>0.1055784338161203</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3974</v>
+        <v>3975</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1024984743724104</v>
+        <v>0.1018322141998453</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1599153121845163</v>
+        <v>0.1592146559353083</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.004510828234195685</v>
+        <v>0.003844002936290281</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.02725802925167642</v>
+        <v>-0.02791561696059119</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.07563192049612155</v>
+        <v>0.07494160021173002</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.08552581216525823</v>
+        <v>0.0848363126281626</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1150086567107778</v>
+        <v>0.1143103833471386</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2394861496776528</v>
+        <v>0.2387505525799511</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1924098649153692</v>
+        <v>0.1916850024501144</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2109161363106793</v>
+        <v>0.2101758593120664</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.07060449293554427</v>
+        <v>0.06989662656807383</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.06885812482549625</v>
+        <v>0.06815077631564748</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1910721622487941</v>
+        <v>0.1903285743167089</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.153137567477259</v>
+        <v>0.1536342990785045</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3984</v>
+        <v>3985</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.09600376135119149</v>
+        <v>0.09537211353768527</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.09919227102997752</v>
+        <v>0.09854085863850059</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.006764244276453724</v>
+        <v>-0.007394028873747516</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.03813026129452624</v>
+        <v>-0.03875099305021479</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.06315087706327915</v>
+        <v>0.06249823637079288</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.07376195295512389</v>
+        <v>0.07310979071267809</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1029556645822254</v>
+        <v>0.1022948907849184</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.2008846207296457</v>
+        <v>0.2001935657499416</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1537637539811172</v>
+        <v>0.1530834735021074</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1951574474739388</v>
+        <v>0.1944565820409707</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.07976173700618716</v>
+        <v>0.07908709389766244</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.07810830730522156</v>
+        <v>0.07743415322472202</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.1989633895713823</v>
+        <v>0.198253696550367</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1617528034589384</v>
+        <v>0.1622199544054723</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.05821714406685174</v>
+        <v>0.05766037563786597</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.02845420228393181</v>
+        <v>0.02788791872195873</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.05405249531253276</v>
+        <v>-0.05460259201856132</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.159363431428396</v>
+        <v>-0.1598862227972333</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.06130065345901414</v>
+        <v>-0.06185371257903682</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.09914118132940786</v>
+        <v>-0.09968200434806818</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.02069577479137052</v>
+        <v>-0.02125729833909418</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.02450851837900814</v>
+        <v>0.02393060660245538</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.002218293563373663</v>
+        <v>0.001645027011818456</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.01417537951357417</v>
+        <v>0.01359002965297407</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1017115049858717</v>
+        <v>-0.1022703516925958</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.05330520964965046</v>
+        <v>-0.05387605892033065</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.06481488950010572</v>
+        <v>0.06420990523783132</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.07895407608189231</v>
+        <v>0.0793874849546512</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4016</v>
+        <v>4017</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02579722210820989</v>
+        <v>0.02528744341105948</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01614000327065668</v>
+        <v>0.01561691338370252</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1169653181914825</v>
+        <v>-0.1174594070622632</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2215897525681854</v>
+        <v>-0.2220568574392985</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1005953060864258</v>
+        <v>-0.1010978781188712</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1622966453548216</v>
+        <v>-0.1627812795298098</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1092107478771212</v>
+        <v>-0.1097096351655864</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.01583071310469109</v>
+        <v>-0.01635755695075858</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.01337705708667158</v>
+        <v>-0.01390535610547516</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.003997230490305981</v>
+        <v>-0.004536308692060231</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1201539756236869</v>
+        <v>-0.1206663954260279</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.0966821551820729</v>
+        <v>-0.09720034095401786</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.01981885672180539</v>
+        <v>0.0192673638483285</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.03465076982639204</v>
+        <v>0.03506275643661638</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4033</v>
+        <v>4034</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.02757008315137455</v>
+        <v>0.02711460944587429</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.01118089748089801</v>
+        <v>0.01071547402910511</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1230260403642873</v>
+        <v>-0.1234618890701569</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2019302526493405</v>
+        <v>-0.2023456941417123</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.08370433826715384</v>
+        <v>-0.08415384662632164</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1191442752399468</v>
+        <v>-0.1195826907984525</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.06662763050497489</v>
+        <v>-0.06707998864481368</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.02511365051172021</v>
+        <v>-0.02558051504074399</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.02292943311549323</v>
+        <v>-0.02339759050973811</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.01717138942069596</v>
+        <v>-0.01764849990119188</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1337045755860586</v>
+        <v>-0.1341548116555131</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1349732899331855</v>
+        <v>-0.1354231433956414</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.02074375465874567</v>
+        <v>-0.02122575787221592</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.02972722525995408</v>
+        <v>-0.02934496834338063</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.07631204689721471</v>
+        <v>0.0759716621497617</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1177542846960264</v>
+        <v>0.117393715853602</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.01897956239569965</v>
+        <v>-0.01930924886729457</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.002157944710297954</v>
+        <v>0.00182372142515419</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1139992934431007</v>
+        <v>0.1136342104764552</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1308781456443455</v>
+        <v>0.1305105850719386</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1821104786000518</v>
+        <v>0.1817296731160596</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2432127995980053</v>
+        <v>0.242813971466731</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1957994108899968</v>
+        <v>0.195411652370467</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.144158239400852</v>
+        <v>0.1437777350744796</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.02679888152370324</v>
+        <v>0.02644572608561901</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.02591951155076089</v>
+        <v>0.02556661414469374</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1349407814724017</v>
+        <v>0.1345583702703408</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1530881423593371</v>
+        <v>0.1533193705394922</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volatility/realized_vol_21.xlsx
+++ b/workspaces/btc_daily_14days/volatility/realized_vol_21.xlsx
@@ -568,53 +568,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 17.23</t>
+          <t>X ≈ 17.24</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>106</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.108523803877361</v>
+        <v>4.079467349114829</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>10.96868097066127</v>
+        <v>10.96759136064052</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.51826737008331</v>
+        <v>11.51820604876563</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.5921370089178</v>
+        <v>12.59173462329092</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>14.88194180534764</v>
+        <v>14.93047219173157</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>14.24097370212137</v>
+        <v>14.26496469063426</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>18.86884391167197</v>
+        <v>18.91686369354363</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>19.34917885411783</v>
+        <v>19.39843396604689</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>21.1777429161851</v>
+        <v>21.25098126020188</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>20.33405244352736</v>
+        <v>20.43335567827815</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>19.19202193280601</v>
+        <v>19.2918940524409</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>18.28834451974179</v>
+        <v>18.41200381094053</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>19.7593195599172</v>
+        <v>19.90798497308494</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>19.99011228650031</v>
+        <v>20.16211104606698</v>
       </c>
     </row>
     <row r="7">
@@ -624,101 +624,101 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.20903442026448</v>
+        <v>-0.9928560949160925</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.297443733607537</v>
+        <v>-1.060959654025432</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.185538123329714</v>
+        <v>-0.950514523570547</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.981720417374191</v>
+        <v>2.201146836558351</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.44510021170602</v>
+        <v>1.713498288152536</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.261999616410826</v>
+        <v>3.498268805459055</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.711737956199627</v>
+        <v>5.959291864751094</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.260628988186589</v>
+        <v>6.504361288153802</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.708595777877086</v>
+        <v>6.97380471746623</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>9.918183085005793</v>
+        <v>10.18903942930392</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>9.209315363179172</v>
+        <v>9.483356786251591</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.709591486738013</v>
+        <v>7.020282809114065</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.799032364089925</v>
+        <v>7.132224667121022</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.057251449415098</v>
+        <v>9.403582363009569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 24.21</t>
+          <t>X ≈ 24.22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2.210563060306058</v>
+        <v>1.987764669629321</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.801827908905018</v>
+        <v>-3.011458220160932</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.196500595494889</v>
+        <v>-3.405155695486741</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.067958929934029</v>
+        <v>-3.277003153316109</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.605800283545335</v>
+        <v>-3.765997862700509</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.73652105353338</v>
+        <v>-3.923113909428281</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.248762279987204</v>
+        <v>-4.41323128580423</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-6.422609639778983</v>
+        <v>-6.593218903930733</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.20471740010619</v>
+        <v>-5.345894214801007</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.201256849054317</v>
+        <v>-5.312742142134312</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-5.406791811237049</v>
+        <v>-5.517740614034977</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.373525603399962</v>
+        <v>-5.46072333691118</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.221959440767925</v>
+        <v>-6.286021191417454</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.715580343721037</v>
+        <v>-4.750837370809315</v>
       </c>
     </row>
     <row r="9">
@@ -731,202 +731,202 @@
         <v>261</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.663935916238088</v>
+        <v>-1.79531869636277</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.123603643047254</v>
+        <v>-2.83662348832501</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.663938076373</v>
+        <v>-3.793838653351536</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-6.063999701827726</v>
+        <v>-5.364382402688754</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.456409378315058</v>
+        <v>-4.886956064012544</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.543704900789038</v>
+        <v>-5.169556795166166</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.012409397227437</v>
+        <v>-5.789000420214968</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.567915256842255</v>
+        <v>-4.518790981792385</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.247476674689594</v>
+        <v>-4.174363035342083</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.245605802532936</v>
+        <v>-6.146417437233865</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-6.451585132478854</v>
+        <v>-6.351798139934921</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.270081573964191</v>
+        <v>-5.14648076288502</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.39325562762162</v>
+        <v>-3.244621154384319</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.93456059718406</v>
+        <v>-3.762561837617397</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 31.19</t>
+          <t>X ≈ 31.2</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>247</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2545509895240841</v>
+        <v>-0.9158032488150809</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.174640661615669</v>
+        <v>1.928065778357599</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.395534062139589</v>
+        <v>3.148440571432339</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.333081856752578</v>
+        <v>4.089951204568585</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>3.393822617402243</v>
+        <v>3.192180500262104</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5.306485498356906</v>
+        <v>5.491324231491419</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.243094746937054</v>
+        <v>7.453979553858524</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>8.799630494210611</v>
+        <v>9.410500832544038</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6.316529897181816</v>
+        <v>6.763189969196596</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.874321042670502</v>
+        <v>6.157031731893269</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.840920897854268</v>
+        <v>3.121940132514482</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.494802591926451</v>
+        <v>4.618409122461486</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.885894609087224</v>
+        <v>5.034529309770676</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.708621185743645</v>
+        <v>4.880619945310308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 34.67</t>
+          <t>X ≈ 34.69</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>257</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.106289718082913</v>
+        <v>4.280809165846478</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.542540210056089</v>
+        <v>1.517568734658646</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.951045002744927</v>
+        <v>-2.378563789850276</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.434952391491684</v>
+        <v>-1.468310741922586</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.4206496313766692</v>
+        <v>-0.7938339473418594</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.676824497270424</v>
+        <v>-1.683798996264613</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.314959423634086</v>
+        <v>-3.298365524379044</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.617474332614968</v>
+        <v>-2.599009297543418</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.7366116430216607</v>
+        <v>-0.6921308063821456</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4194852867864398</v>
+        <v>-0.3551595550375666</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.5428082967328436</v>
+        <v>0.8180012940810855</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.2000403368986525</v>
+        <v>0.09881772980120473</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.00875330962117</v>
+        <v>-0.8601356117909233</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.172063765185008</v>
+        <v>-1.000065005618254</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 38.16</t>
+          <t>X ≈ 38.17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.484841580887363</v>
+        <v>-3.495860793038688</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.474646035438262</v>
+        <v>-0.4748061111727182</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.106918610543438</v>
+        <v>2.091020194660018</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.9158226417580835</v>
+        <v>0.9054715182352453</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.6190482160843302</v>
+        <v>-0.5700769709202902</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.644080111021339</v>
+        <v>-1.612753137111994</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.728114120230849</v>
+        <v>-1.673467161079792</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.865098853339063</v>
+        <v>-1.81042725836771</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.577702629291444</v>
+        <v>-5.464376363074663</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.780364310301408</v>
+        <v>-3.657368475981684</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.330133114090899</v>
+        <v>-2.21723251015414</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.115078224042698</v>
+        <v>-1.172665038786555</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3078756619565439</v>
+        <v>0.07638102958550519</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.05010100335565</v>
+        <v>0.3259640748648778</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.695003732147292</v>
+        <v>-2.668820518828845</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.417454946178765</v>
+        <v>-3.342649649617925</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.714233330862264</v>
+        <v>-2.82261403447081</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-4.283378590753507</v>
+        <v>-4.521014808362274</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-4.66381155532526</v>
+        <v>-5.011862100376469</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.628157587740802</v>
+        <v>-3.213456990684186</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.167501520218941</v>
+        <v>-3.883377438682331</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-5.030229107931639</v>
+        <v>-5.873969247059328</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.425246196203815</v>
+        <v>-3.473146812923005</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-6.54454299461645</v>
+        <v>-7.652355016082772</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.57744500239113</v>
+        <v>-7.857601875892506</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.605566850035878</v>
+        <v>-6.884063384003653</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.713217703349137</v>
+        <v>-6.974835000575347</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.237482053122825</v>
+        <v>-5.338349147214693</v>
       </c>
     </row>
     <row r="14">
@@ -991,150 +991,150 @@
         <v>284</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-6.706268143210409</v>
+        <v>-6.73546393756304</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.543211536522158</v>
+        <v>-5.543364926526479</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-5.76509906899021</v>
+        <v>-5.765593561368213</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.247050593916889</v>
+        <v>-5.198504674151117</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-6.006014592450818</v>
+        <v>-5.982057183501205</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-5.386499599604306</v>
+        <v>-5.338487920613986</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.853568243390967</v>
+        <v>-5.80432068099725</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.970888428083001</v>
+        <v>-6.897631318303304</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-8.877145252581712</v>
+        <v>-8.777797927287139</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-9.786071762954663</v>
+        <v>-9.686163726935987</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-11.16014431482461</v>
+        <v>-11.03644769379636</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-9.467619111799991</v>
+        <v>-9.318929564022163</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-8.5376581094607</v>
+        <v>-8.365659349894038</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 48.62</t>
+          <t>X ≈ 48.64</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>268</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.623561581405909</v>
+        <v>1.594365787053277</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3855098167003703</v>
+        <v>0.3843230302557146</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.009261568054796498</v>
+        <v>-0.009414958059117851</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.744708066257481</v>
+        <v>-1.745202558635484</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.7904603059202557</v>
+        <v>-0.7419143861544839</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.8662206046433312</v>
+        <v>-0.8422631956937181</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.5777966355513371</v>
+        <v>-0.5297849565610164</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.07453770573658858</v>
+        <v>0.1237852681303053</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.852116092577184</v>
+        <v>-1.778858982797487</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.8363632471160827</v>
+        <v>-0.7370159218215093</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.787333062092692</v>
+        <v>-1.687425026074017</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.752954909737369</v>
+        <v>-1.629258288709124</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.426837106334446</v>
+        <v>-1.278147558556618</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.813041754615291</v>
+        <v>-3.641042995048629</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 52.11</t>
+          <t>X ≈ 52.12</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>205</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.641035188977902</v>
+        <v>2.611839394625271</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.517653973962744</v>
+        <v>1.516467187518089</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.537516735549218</v>
+        <v>4.537363345544897</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.692132123040018</v>
+        <v>3.691637630662015</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.178232813846762</v>
+        <v>2.226778733612534</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4512224248108296</v>
+        <v>-0.4272650158612166</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.4396769720206208</v>
+        <v>0.4876886510109415</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.923827840428885</v>
+        <v>1.973075402822602</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.890975668064172</v>
+        <v>5.990322993358745</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>8.125298900047824</v>
+        <v>8.225206936066499</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>8.159677052403147</v>
+        <v>8.283373673431392</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.812696930797053</v>
+        <v>4.96138647857488</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.06282282492608</v>
+        <v>4.234821584492742</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>218</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.023671125429004</v>
+        <v>2.994475331076373</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>5.082209803007324</v>
+        <v>5.081023016562668</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.770007225591726</v>
+        <v>3.769853835587405</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.065369983859043</v>
+        <v>2.06487549148104</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1509336417724754</v>
+        <v>0.1994795615382472</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.38655471391359</v>
+        <v>-1.362597304963977</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.306127458500917</v>
+        <v>-3.258115779510597</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.938333716966397</v>
+        <v>-1.889086154572681</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.586471836791972</v>
+        <v>-6.513214727012276</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.849234669819189</v>
+        <v>-2.749887344524616</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.971367020739827</v>
+        <v>-3.871458984721151</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.18469529040285</v>
+        <v>-1.060998669374605</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.146130547385987</v>
+        <v>-0.997440999608159</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.755257282480649</v>
+        <v>-2.583258522913987</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>140</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.052344601962929</v>
+        <v>-1.08154039631556</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.377816409312473</v>
+        <v>-3.379003195757129</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.915444936924651</v>
+        <v>-5.915598326928972</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.928076936193513</v>
+        <v>-2.928571428571516</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.609223632146346</v>
+        <v>-0.5606777123805742</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.740421031082604</v>
+        <v>-1.716463622132991</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.25370281892021</v>
+        <v>-3.20569113992989</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.29220003413559</v>
+        <v>-2.242952471741873</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.218246380770204</v>
+        <v>1.2915034905499</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>6.082613298726216</v>
+        <v>6.181960624020789</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>8.735054997608884</v>
+        <v>8.83496303362756</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>10.19800457853547</v>
+        <v>10.32170119956371</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.206425153793568</v>
+        <v>6.355114701571395</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.003589375448676</v>
+        <v>5.175588135015339</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>145</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.00184259015527</v>
+        <v>1.972646795802639</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>6.597553048815612</v>
+        <v>6.596366262370957</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.004114887663597244</v>
+        <v>-0.004268277667918596</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.253200088902794</v>
+        <v>-1.253694581280797</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4121792971707805</v>
+        <v>-0.3636333774050087</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.494115612363402</v>
+        <v>-1.470158203413789</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.578825971629485</v>
+        <v>-1.530814292639164</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.781691591480254</v>
+        <v>2.83093915387397</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.341399090129997</v>
+        <v>1.414656199909693</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>4.039103481163565</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.9764343079535109</v>
+        <v>1.076342343972186</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.39012280513662</v>
+        <v>2.513819426164865</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.28031677940934</v>
+        <v>1.429006327187167</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.252568260019231</v>
+        <v>-1.080569500452569</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>92</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.866910056422043</v>
+        <v>1.837714262069412</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.005145601859049</v>
+        <v>-3.006332388303704</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.226003943135773</v>
+        <v>-1.226157333140094</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.1827353212866</v>
+        <v>-2.183229813664603</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.721024874382351</v>
+        <v>-2.672478954616579</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.924175242209316</v>
+        <v>1.948132651158929</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.752508361204022</v>
+        <v>0.8005200401943426</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2854397174172831</v>
+        <v>0.3346872798109999</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2244575608943862</v>
+        <v>0.2977146706740825</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-5.177988480651941</v>
+        <v>-5.078080444633265</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-7.31752337177501</v>
+        <v>-7.193826750746766</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-7.737674225088355</v>
+        <v>-7.588984677310528</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-10.77280814007934</v>
+        <v>-10.60080938051268</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>103</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>6.742384940339484</v>
+        <v>6.713189145986853</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.218577488052304</v>
+        <v>2.217390701607648</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.823806103297265</v>
+        <v>1.823652713292944</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9831574604778552</v>
+        <v>0.9826629680998522</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.299236839420999</v>
+        <v>5.347782759186771</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>6.567484655463851</v>
+        <v>6.591442064413464</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.541026723382146</v>
+        <v>4.589038402372466</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.044831866003179</v>
+        <v>5.094079428396896</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>6.925597282296046</v>
+        <v>6.998854392075742</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.163057126742771</v>
+        <v>3.262404452037345</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.987482182074757</v>
+        <v>2.087390218093432</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.08011276161455072</v>
+        <v>0.2038093826427954</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.543457053932208</v>
+        <v>3.692146601710036</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.769192704158847</v>
+        <v>3.941191463725509</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>99</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.054437504819184</v>
+        <v>1.025241710466553</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4533524218563585</v>
+        <v>0.4521656354117027</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>7.129288107808392</v>
+        <v>7.129134717804071</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4.22921022109373</v>
+        <v>4.228715728715727</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3494833724060129</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.08241237307395</v>
+        <v>-3.058454964124337</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.146920712138098</v>
+        <v>-1.098909033147777</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4062126642771844</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6648705023466661</v>
+        <v>-0.5916133925669698</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-7.575395359282524</v>
+        <v>-7.476048033987951</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.759894497340696</v>
+        <v>-5.659986461322021</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.735617355086326</v>
+        <v>-6.611920734058081</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-7.155768208399792</v>
+        <v>-7.007078660621964</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.909830537971239</v>
+        <v>-4.737831778404576</v>
       </c>
     </row>
     <row r="23">
@@ -1459,150 +1459,150 @@
         <v>96</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.685750636132312</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.116231209735211</v>
+        <v>1.115044423290556</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.804793158313444</v>
+        <v>2.804639768309123</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.060018301901806</v>
+        <v>6.059523809523803</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.355062082139447</v>
+        <v>1.403608001905219</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>5.819102778441142</v>
+        <v>5.843060187390755</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6.776059085841702</v>
+        <v>6.824070764832022</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.142323775388292</v>
+        <v>2.191571337782008</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.164674952198908</v>
+        <v>4.237932061978604</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.356422822535656</v>
+        <v>4.455770147830229</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.068388330942192</v>
+        <v>2.168296366960867</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.01943314996412226</v>
+        <v>0.1431297709923669</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.765948963317378</v>
+        <v>3.914638511095205</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.950017946877246</v>
+        <v>3.122016706443908</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 80.03</t>
+          <t>X ≈ 80.02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-10.17322372284205</v>
+        <v>-10.76253900935301</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-6.015179046675158</v>
+        <v>-6.520473376062306</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-7.371488892968607</v>
+        <v>-7.885085150784725</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-4.842579750346744</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.010322533245166</v>
+        <v>-2.419207532075333</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.7514100420715693</v>
+        <v>-1.175548226848633</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.759197324414707</v>
+        <v>-3.177951888889666</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-6.110881352816861</v>
+        <v>-6.556406008496303</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.248786586262746</v>
+        <v>-4.651631044817627</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.137166921054082</v>
+        <v>-3.533712052817016</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.226483463929718</v>
+        <v>-6.650473859576465</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-5.621433335803751</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.843025395656973</v>
+        <v>-1.162222330328746</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.3057871776464722</v>
+        <v>0.05769631809439346</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 83.52</t>
+          <t>X ≈ 83.5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.519083969465655</v>
+        <v>4.068835543534064</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.907897876401826</v>
+        <v>2.485658458378211</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1797931583134442</v>
+        <v>0.7761309963793082</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3100183019018061</v>
+        <v>0.9060150375939884</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.771728748806083</v>
+        <v>4.364134317694621</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.402436111774541</v>
+        <v>2.005340889145245</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.98439241917503</v>
+        <v>4.576263747288152</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.183990442054998</v>
+        <v>2.794641513220611</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.456341618865515</v>
+        <v>4.073458377768013</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.939756155868992</v>
+        <v>3.24962979695303</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.068388330942128</v>
+        <v>4.361278823101159</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.563900183369206</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-8.650717703349287</v>
+        <v>-9.133607102939884</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-11.09164871978945</v>
+        <v>-10.20035171460876</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>47</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.093552054572029</v>
+        <v>7.064356260219398</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>9.737685110444374</v>
+        <v>9.736498323999719</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>7.215254151221195</v>
+        <v>7.215100761216874</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>9.473138869277754</v>
+        <v>9.472644376899751</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11.06250889065014</v>
+        <v>11.11105481041592</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>13.4875424947532</v>
+        <v>13.51149990370281</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.147512986550858</v>
+        <v>9.195524665541178</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.552784768296092</v>
+        <v>6.602032330689809</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.364143037305176</v>
+        <v>4.437400147084873</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.641883815443457</v>
+        <v>5.74123114073803</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>13.9478209550556</v>
+        <v>14.04772899107428</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>13.98219910741093</v>
+        <v>14.10589572843917</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>15.68970782856562</v>
+        <v>15.83839737634344</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>18.04310305326029</v>
+        <v>18.21510181282695</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>35</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-6.766630316248637</v>
+        <v>-6.795826110601269</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.663530695026758</v>
+        <v>-2.664717481471413</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.058302079781633</v>
+        <v>-3.058455469785955</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.643351635235064</v>
+        <v>5.642857142857061</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.962204939282302</v>
+        <v>8.010750859048073</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>11.11672182606033</v>
+        <v>11.14067923500994</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.365737431498687</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.781753619229633</v>
+        <v>-3.708496509449937</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.631672415559585</v>
+        <v>-4.532325090265012</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.836373573819778</v>
+        <v>-4.736465537801102</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.9122902928211829</v>
+        <v>1.035986913849428</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>6.432160804020022</v>
+        <v>6.604159563586684</v>
       </c>
     </row>
     <row r="28">
@@ -1719,98 +1719,98 @@
         <v>25</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>11.5190839694657</v>
+        <v>11.48988817511307</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.907897876401762</v>
+        <v>5.906711089957106</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>9.513126491646723</v>
+        <v>9.512973101642402</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9.643351635235085</v>
+        <v>9.642857142857082</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9.105062082139391</v>
+        <v>9.153608001905162</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.402436111774591</v>
+        <v>5.426393520724204</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.317725752508423</v>
+        <v>9.365737431498744</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.850657108721627</v>
+        <v>8.899904671115344</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>12.78967495219885</v>
+        <v>12.86293206197855</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>23.93975615586905</v>
+        <v>24.03910348116362</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>27.7350549976088</v>
+        <v>27.83496303362747</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>19.76943314996424</v>
+        <v>19.89312977099248</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>23.34928229665071</v>
+        <v>23.49797184442854</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>19.57501794687736</v>
+        <v>19.74701670644402</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 97.47</t>
+          <t>X ≈ 97.45</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>32</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-11.8559160305344</v>
+        <v>-11.88511182488703</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-7.217102123598139</v>
+        <v>-7.218288910042794</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-4.486873508353263</v>
+        <v>-4.487026898357584</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.231648364764816</v>
+        <v>-1.232142857142819</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.60506208213949</v>
+        <v>7.653608001905262</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.472563888225508</v>
+        <v>-1.448606479275895</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.692725752508409</v>
+        <v>4.740737431498729</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.225657108721627</v>
+        <v>4.274904671115344</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>13.53967495219881</v>
+        <v>13.6129320619785</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>18.93975615586895</v>
+        <v>19.03910348116352</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>24.98505499760884</v>
+        <v>25.08496303362752</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>21.89443314996416</v>
+        <v>22.01812977099241</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.09928229665071</v>
+        <v>12.24797184442854</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.075017946877203</v>
+        <v>6.247016706443866</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>10</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-24.09210212359818</v>
+        <v>-24.09328891004284</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-4.486873508353078</v>
+        <v>-4.487026898357399</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-4.356648364764716</v>
+        <v>-4.357142857142719</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-15.14934289127837</v>
+        <v>-15.10009532888466</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-15.21032504780101</v>
+        <v>-15.13706793802131</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.73505499760865</v>
+        <v>3.834963033627325</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.769433149963973</v>
+        <v>3.893129770992218</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.57501794687753</v>
+        <v>3.747016706444192</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>20</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-7.480916030534281</v>
+        <v>-7.510111824886913</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-14.09210212359818</v>
+        <v>-14.09328891004284</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-9.486873508353291</v>
+        <v>-9.487026898357612</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-24.35664836476493</v>
+        <v>-24.35714285714294</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-24.89493791786055</v>
+        <v>-24.84639199809478</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-34.59756388822554</v>
+        <v>-34.57360647927592</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-24.68227424749163</v>
+        <v>-24.63426256850131</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-35.14934289127837</v>
+        <v>-35.10009532888466</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-30.21032504780115</v>
+        <v>-30.13706793802145</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-36.06024384413108</v>
+        <v>-35.96089651883651</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-36.2649450023912</v>
+        <v>-36.16503696637253</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-26.23056685003588</v>
+        <v>-26.10687022900763</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-26.65071770334929</v>
+        <v>-26.50202815557146</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-16.42498205312283</v>
+        <v>-16.25298329355616</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>12</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-10.81424936386768</v>
+        <v>-10.84344515822031</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-21.15354017502001</v>
+        <v>-21.15369356502433</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-21.02331503143153</v>
+        <v>-21.02380952380953</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-13.22827125119388</v>
+        <v>-13.17972533142811</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-21.26423055489201</v>
+        <v>-21.2402731459424</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-29.68227424749163</v>
+        <v>-29.63426256850131</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-13.48267622461183</v>
+        <v>-13.43342866221811</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.060243844130888</v>
+        <v>-5.960896518836314</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-14.56390018336921</v>
+        <v>-14.44020356234096</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-14.98405103668262</v>
+        <v>-14.83536148890479</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-14.75831538645621</v>
+        <v>-14.58631662688955</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>17</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.4602604400537942</v>
+        <v>0.4310646457011629</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.150925653009864</v>
+        <v>-1.15211243945452</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.545697037764981</v>
+        <v>-1.545850427769302</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.466881046999852</v>
+        <v>4.466386554621849</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.928591493904065</v>
+        <v>3.977137413669837</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.10831846471571</v>
+        <v>10.13227587366532</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.02360810544954</v>
+        <v>10.07161978443986</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.208166420690134</v>
+        <v>-2.158918858296417</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.26914857721291</v>
+        <v>-2.195891467433214</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.119067373542769</v>
+        <v>-3.019720048248196</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.323768531802962</v>
+        <v>-3.223860495784287</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.171743320624117</v>
+        <v>-9.048046699595872</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.591894173937526</v>
+        <v>-9.443204626159698</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-15.24851146488738</v>
+        <v>-15.07651270532072</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>40</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.01908396946564</v>
+        <v>4.989888175113009</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.90789787640179</v>
+        <v>10.90671108995713</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.51312649164681</v>
+        <v>10.51297310164249</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>20.64335163523514</v>
+        <v>20.64285714285714</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>20.10506208213948</v>
+        <v>20.15360800190525</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>25.40243611177453</v>
+        <v>25.42639352072415</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>25.31772575250837</v>
+        <v>25.36573743149869</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>27.35065710872167</v>
+        <v>27.39990467111539</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>22.28967495219885</v>
+        <v>22.36293206197855</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>16.43975615586899</v>
+        <v>16.53910348116356</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.2350549976088</v>
+        <v>16.33496303362747</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.26943314996412</v>
+        <v>16.39312977099237</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>15.84928229665071</v>
+        <v>15.99797184442854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.57501794687722</v>
+        <v>18.74701670644388</v>
       </c>
     </row>
   </sheetData>
@@ -2210,157 +2210,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 15.49</t>
+          <t>X &gt; 15.5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4074</v>
+        <v>4085</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2665778851954741</v>
+        <v>-0.2651142651017295</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1273444143470854</v>
+        <v>-0.1269720928595319</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2396274863213961</v>
+        <v>-0.2389800233575414</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2430342609450733</v>
+        <v>-0.2423687423687468</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3027263087495982</v>
+        <v>-0.3031579971177436</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3349475236982684</v>
+        <v>-0.3346619398182398</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.283842490569306</v>
+        <v>-0.2843114443566463</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.345421322650914</v>
+        <v>-0.3457565364133757</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2703887889141683</v>
+        <v>-0.2715422656498134</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2976151045527828</v>
+        <v>-0.2993655821771029</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.2924161821802613</v>
+        <v>-0.2941954790926857</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.34244123668946</v>
+        <v>-0.3446974861644705</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.3071594211407032</v>
+        <v>-0.3101534614941244</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3130527453171581</v>
+        <v>-0.3166307843761587</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 18.98</t>
+          <t>X &gt; 18.99</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3968</v>
+        <v>3979</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3834530815265609</v>
+        <v>-0.3808533078529095</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.4237604150554688</v>
+        <v>-0.4225297018243523</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.5537244759330164</v>
+        <v>-0.5521898056257157</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.5859092999081454</v>
+        <v>-0.5842674497725895</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.7083651242975577</v>
+        <v>-0.7089797613846542</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.724324451605753</v>
+        <v>-0.7235939385183912</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.7954817946614412</v>
+        <v>-0.795828047678441</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.8715371539859689</v>
+        <v>-0.8717389926236834</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.8433479524072425</v>
+        <v>-0.8448992633226595</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.8487634815932381</v>
+        <v>-0.8516823586556725</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.8129178052116472</v>
+        <v>-0.8159661476884494</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.8401386384489697</v>
+        <v>-0.844373368922227</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.84320951488872</v>
+        <v>-0.8487618239131649</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.8554256015098574</v>
+        <v>-0.8621815845839862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 22.47</t>
+          <t>X &gt; 22.48</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3771</v>
+        <v>3781</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3403240643609848</v>
+        <v>-0.3488044975280005</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.3781185127073527</v>
+        <v>-0.389096977535587</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.5207180350586711</v>
+        <v>-0.5313306958259005</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.7200442917682963</v>
+        <v>-0.7301315144892087</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.8208638437864764</v>
+        <v>-0.8358379083850167</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.9325731499349104</v>
+        <v>-0.9446806413238846</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.135424062208408</v>
+        <v>-1.149574078532993</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.244127111559024</v>
+        <v>-1.258003963687933</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.237867420682505</v>
+        <v>-1.254342106008771</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.411237221614449</v>
+        <v>-1.429852925705653</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.336487132756858</v>
+        <v>-1.355311807810153</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.234542466256393</v>
+        <v>-1.25622259485484</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.242446229330199</v>
+        <v>-1.266702930822646</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.373271631483931</v>
+        <v>-1.399769857957047</v>
       </c>
     </row>
     <row r="9">
@@ -2370,205 +2370,205 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3537</v>
+        <v>3548</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.5090850446188639</v>
+        <v>-0.502248865044244</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2177713261904586</v>
+        <v>-0.2168844156608145</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3436942524343962</v>
+        <v>-0.3426043077422065</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5647115167242589</v>
+        <v>-0.562876415321611</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.636618684922027</v>
+        <v>-0.6434119587357756</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.7470702351930285</v>
+        <v>-0.7490845445177001</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.9294525770627402</v>
+        <v>-0.9352470973339493</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.901530303076278</v>
+        <v>-0.9076361279842686</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.9754295085577809</v>
+        <v>-0.9856466039375817</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.16049800962098</v>
+        <v>-1.174860482800398</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.067204889396848</v>
+        <v>-1.081961776285233</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.9607166098550408</v>
+        <v>-0.9801096656273458</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.9130127853165035</v>
+        <v>-0.9370802829312765</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.152151971132369</v>
+        <v>-1.179702572022833</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 29.44</t>
+          <t>X &gt; 29.45</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3276</v>
+        <v>3287</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.337407365286559</v>
+        <v>-0.3995743210910589</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.01373729246022037</v>
+        <v>-0.008867409891003319</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.0005009972750045222</v>
+        <v>-0.0685634911300852</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1265814140649155</v>
+        <v>-0.1816190186976812</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2526243714374132</v>
+        <v>-0.3064588064761935</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3649207700768642</v>
+        <v>-0.3980826408306726</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.5244917315001629</v>
+        <v>-0.5498410683494797</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6094282051114064</v>
+        <v>-0.6208970294616378</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.7147444321351983</v>
+        <v>-0.7324506840724823</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7553657953505137</v>
+        <v>-0.7801004082317533</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.6382295403600935</v>
+        <v>-0.663517209533623</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.617388082494692</v>
+        <v>-0.6492843366391341</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.7154110204075792</v>
+        <v>-0.7538529730897068</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.9304765586172579</v>
+        <v>-0.9746139598171197</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 32.93</t>
+          <t>X &gt; 32.94</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3029</v>
+        <v>3040</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3441638937822091</v>
+        <v>-0.3576307207134732</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1624737118915078</v>
+        <v>-0.166243231436205</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2763471925637475</v>
+        <v>-0.329945071213281</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4902449425865143</v>
+        <v>-0.528684099338065</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5499741258921489</v>
+        <v>-0.5907232501486774</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.8273959593482871</v>
+        <v>-0.8765969492068493</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.157900070943548</v>
+        <v>-1.200151493903881</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.376690502481011</v>
+        <v>-1.435948105749596</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.288110149976497</v>
+        <v>-1.341471487150599</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-1.29598403536081</v>
+        <v>-1.34374239461691</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.9219370868239238</v>
+        <v>-0.9710856185750245</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.034262000151351</v>
+        <v>-1.077284430191064</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.172169848563811</v>
+        <v>-1.224159033572114</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.390317147213217</v>
+        <v>-1.450351714608722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 36.42</t>
+          <t>X &gt; 36.43</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2772</v>
+        <v>2783</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.7567780994998685</v>
+        <v>-0.7859738938524998</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.3205503994602452</v>
+        <v>-0.321737185904901</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1210811978968778</v>
+        <v>-0.1407625305414513</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4026584294665199</v>
+        <v>-0.4419129720853903</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.5619641674110767</v>
+        <v>-0.5719667107384581</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.748643024916106</v>
+        <v>-0.8020547551379167</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.9579129664552823</v>
+        <v>-1.006389005282927</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.261653906397164</v>
+        <v>-1.32854360474672</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.339241144308168</v>
+        <v>-1.401435754113407</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.37724672597539</v>
+        <v>-1.435034449870919</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.057737795183989</v>
+        <v>-1.136301334188616</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.111605062004152</v>
+        <v>-1.185893217513382</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.187320660435475</v>
+        <v>-1.257775282008247</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.410552038692735</v>
+        <v>-1.49193406610371</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2471</v>
+        <v>2479</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4244644176311354</v>
+        <v>-0.4536602119837667</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3017795429530139</v>
+        <v>-0.3029663293976697</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3924806079901657</v>
+        <v>-0.4144462531962461</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.5632666052814059</v>
+        <v>-0.6071428571428612</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5550105864112211</v>
+        <v>-0.5721984497076846</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6395671192432388</v>
+        <v>-0.7026387373403722</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.8640924293098138</v>
+        <v>-0.9245851491464734</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.188146448271098</v>
+        <v>-1.269450167594329</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.8229413033611976</v>
+        <v>-0.9031969702795166</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.0845156887912</v>
+        <v>-1.162509422062243</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.9027434645522732</v>
+        <v>-1.003746643791878</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.111181985608518</v>
+        <v>-1.187515390297953</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.369455056647539</v>
+        <v>-1.421382994281139</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.710291644381357</v>
+        <v>-1.714863083794093</v>
       </c>
     </row>
     <row r="14">
@@ -2633,150 +2633,150 @@
         <v>2151</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.0866807911108296</v>
+        <v>-0.1158765854634609</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.161733301785361</v>
+        <v>0.1605465153407053</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.04707806437367879</v>
+        <v>-0.04723145437800014</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.00983293008331998</v>
+        <v>-0.01032742246132301</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.05624757725799867</v>
+        <v>0.1047934970237705</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.3437284628419235</v>
+        <v>-0.3197710538923104</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5214188314060948</v>
+        <v>-0.4734071524157741</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6165674380008213</v>
+        <v>-0.5673198756071045</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5845695852256085</v>
+        <v>-0.5113124754459122</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2722382653304507</v>
+        <v>-0.1728909400358773</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.05852938174964351</v>
+        <v>0.04137865426903176</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.44256127123532</v>
+        <v>-0.3188646502070753</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.7232421106017313</v>
+        <v>-0.5745525628239037</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.334326544057198</v>
+        <v>-1.162327784490536</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 46.88</t>
+          <t>X &gt; 46.89</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1867</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9202623304726103</v>
+        <v>0.891066536119979</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.8088084280890158</v>
+        <v>0.80762164164436</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7889700910040318</v>
+        <v>0.7888167009997105</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.8656333706395287</v>
+        <v>0.8651388782615257</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.8629624570724914</v>
+        <v>0.9115083768382632</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5175941192731983</v>
+        <v>0.5415515282228114</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.218636304195563</v>
+        <v>0.2666479831858837</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1800625720317512</v>
+        <v>0.229310134425468</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3868897352733072</v>
+        <v>0.4601468450530035</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.036703129623682</v>
+        <v>1.136050454918255</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.421182474845004</v>
+        <v>1.521090510863679</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.187751307436002</v>
+        <v>1.311447928464247</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6069148622639915</v>
+        <v>0.7556044100418191</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2385867665667831</v>
+        <v>-0.0665880070001208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 50.37</t>
+          <t>X &gt; 50.38</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1599</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.802386033255523</v>
+        <v>0.7731902389028917</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.879755287283615</v>
+        <v>0.8785685008389592</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9227575110339004</v>
+        <v>0.922604121029579</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.303139002339584</v>
+        <v>1.302644509961581</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.140083970819873</v>
+        <v>1.188629890585645</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7495280442323136</v>
+        <v>0.7734854531819266</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.3521222503194963</v>
+        <v>0.4001339293098169</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1977490411794065</v>
+        <v>0.2469966035731233</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7621577539499427</v>
+        <v>0.835414863729639</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.350637956994696</v>
+        <v>1.449985282289269</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.958944928815804</v>
+        <v>2.058852964834479</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.680627646524471</v>
+        <v>1.804324267552715</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9477813585644128</v>
+        <v>1.09647090634224</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3605088787096378</v>
+        <v>0.5325076382763001</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1394</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5319964515316471</v>
+        <v>0.5028006571790158</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7859466568896281</v>
+        <v>0.7847598704449723</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3911752721345891</v>
+        <v>0.3910218821302678</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9518164845895214</v>
+        <v>0.9513219922115184</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.9874150233159185</v>
+        <v>1.03596094308169</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.9261089955621884</v>
+        <v>0.9500664045118015</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3392465559516893</v>
+        <v>0.3872582349420099</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.05608607635728191</v>
+        <v>-0.006838513963565163</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1698758130309912</v>
+        <v>0.2431329228106875</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6829412347785961</v>
+        <v>0.7822885600731695</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.052128168340502</v>
+        <v>1.152036204359177</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.7278262633070227</v>
+        <v>0.8515228843352673</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.3794114214713744</v>
+        <v>0.528100969249202</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1839490545574805</v>
+        <v>-0.01195029499081812</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1176</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.07010437762890831</v>
+        <v>0.040908583276277</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.01046947053695391</v>
+        <v>-0.01165625698160966</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.2351728280811116</v>
+        <v>-0.235326218085433</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7453924515616634</v>
+        <v>0.7448979591836604</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.142477048125848</v>
+        <v>1.19102296789162</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.35481706415549</v>
+        <v>1.378774473105103</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.015004664072997</v>
+        <v>1.063016343063317</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.2928339794699184</v>
+        <v>0.3420815418636352</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.422328013423339</v>
+        <v>1.495585123203035</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.33771533954247</v>
+        <v>1.437062664837043</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.983354317336691</v>
+        <v>2.083262353355366</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.082358320032149</v>
+        <v>1.206054941060394</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.6622074667187405</v>
+        <v>0.8108970144965681</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.2927050217071852</v>
+        <v>0.4647037812738475</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1036</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2217866721683421</v>
+        <v>0.1925908778157108</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.4445774130813547</v>
+        <v>0.4433906266366989</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5324315109518025</v>
+        <v>0.5322781209474812</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.241807233690743</v>
+        <v>1.24131274131274</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.379193356270726</v>
+        <v>1.427739276036498</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.773092482430904</v>
+        <v>1.797049891380517</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.591857026639644</v>
+        <v>1.639868705629965</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6421629002274187</v>
+        <v>0.6914104626211355</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.449906612430517</v>
+        <v>1.523163722210214</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.6965129126257494</v>
+        <v>0.7958602379203228</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.070962333516128</v>
+        <v>1.170870369534804</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.1494857689547899</v>
+        <v>-0.0257891479265453</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.08701113964272622</v>
+        <v>0.06167840813510139</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3439009720416664</v>
+        <v>-0.171902212475004</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>891</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.06789695084861336</v>
+        <v>-0.09709274520124467</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5567485882446448</v>
+        <v>-0.5579353746893005</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6197482649352253</v>
+        <v>0.6195948749309039</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.647840973057811</v>
+        <v>1.647346480679808</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.670718647796008</v>
+        <v>1.71926456756178</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.304793014131434</v>
+        <v>2.328750423081047</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.107849209298486</v>
+        <v>2.155860888288807</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2939792187104047</v>
+        <v>0.3432267811041214</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.467564963422191</v>
+        <v>1.540822073201888</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1687123848252199</v>
+        <v>0.2680597101197932</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.086345682232825</v>
+        <v>1.1862537182515</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5627778489135409</v>
+        <v>-0.4390812278852962</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3095280288262785</v>
+        <v>-0.1608384810484509</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1960258241665258</v>
+        <v>-0.02402706459986348</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>799</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2906782332877853</v>
+        <v>-0.3198740276404166</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.2748305341113237</v>
+        <v>-0.2760173205559795</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8322754278169953</v>
+        <v>0.8321220378126739</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.088908581417869</v>
+        <v>2.088414089039865</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.176401256106907</v>
+        <v>2.224947175872678</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.348618840185047</v>
+        <v>2.37257624913466</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.263908480918879</v>
+        <v>2.311920159909199</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.294962490448782</v>
+        <v>0.3442100528424987</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.610701235052424</v>
+        <v>1.683958344832121</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.8859388842795042</v>
+        <v>0.9852862095740775</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.807645736031823</v>
+        <v>1.907553772050498</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2149900961468489</v>
+        <v>0.3386867171750936</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.545777916175112</v>
+        <v>0.6944674639529396</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.021826457515552</v>
+        <v>1.193825217082214</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>696</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.33149074317803</v>
+        <v>-1.360686537530661</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.6438262615292203</v>
+        <v>-0.645013047973876</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.6855402847502248</v>
+        <v>0.6853868947459034</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.252547037533994</v>
+        <v>2.252052545155991</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.714257484438299</v>
+        <v>1.762803404204071</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.724275192234302</v>
+        <v>1.748232601183915</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.926921154807218</v>
+        <v>1.974932833797538</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4079635809335471</v>
+        <v>-0.3587160185398304</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8241577108195344</v>
+        <v>0.8974148205992307</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.5489515581678432</v>
+        <v>0.6482988834624166</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.78103200910305</v>
+        <v>1.880940045121726</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.234950391343439</v>
+        <v>0.3586470123716836</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1021558598691001</v>
+        <v>0.2508454076469278</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.6152478319347168</v>
+        <v>0.7872465915013791</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>597</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.727147186313246</v>
+        <v>-1.756342980665877</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.825770465306725</v>
+        <v>-0.8269572517513808</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3830209120383117</v>
+        <v>-0.383174302042633</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.924758670411023</v>
+        <v>1.92426417803302</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.056485867734082</v>
+        <v>2.105031787499854</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.521364084973861</v>
+        <v>2.545321493923474</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.436653725707693</v>
+        <v>2.484665404698013</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5429777321493958</v>
+        <v>-0.4937301697556791</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.071081987374733</v>
+        <v>1.144339097154429</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.896205067091771</v>
+        <v>1.995552392386344</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.031537409669099</v>
+        <v>3.131445445687774</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.390873685977525</v>
+        <v>1.514570307005769</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.305731207873492</v>
+        <v>1.45442075565132</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.531466858100025</v>
+        <v>1.703465617666687</v>
       </c>
     </row>
     <row r="24">
@@ -3153,150 +3153,150 @@
         <v>501</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.381115631332754</v>
+        <v>-2.410311425685386</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.197890546751879</v>
+        <v>-1.199077333196534</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9938595362973288</v>
+        <v>-0.9940129263016502</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.132373591322967</v>
+        <v>1.131879098944964</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.190890425452821</v>
+        <v>2.239436345218593</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.889462059878333</v>
+        <v>1.913419468827946</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.605150902208962</v>
+        <v>1.653162581199282</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.057526524012907</v>
+        <v>-1.00827896161919</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4782977066898653</v>
+        <v>0.5515548164695616</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.42478609598875</v>
+        <v>1.524133421283324</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.216092921760492</v>
+        <v>3.316000957779167</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.653664686890266</v>
+        <v>1.777361307918511</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8343122367704723</v>
+        <v>0.9830017845482999</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.259648685400201</v>
+        <v>1.431647444966863</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 81.77</t>
+          <t>X &gt; 81.76</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3398580960255373</v>
+        <v>-0.2488052922236648</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.06406916103657778</v>
+        <v>0.1780678738767634</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6768544513445107</v>
+        <v>0.7893550111901959</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2.570303776293073</v>
+        <v>2.67803302225412</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.291460067026101</v>
+        <v>3.445065288337375</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.581277421598216</v>
+        <v>2.712825681528173</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.748456231097784</v>
+        <v>2.903425873709743</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.2662742371851081</v>
+        <v>0.4275428620701192</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.716627093256783</v>
+        <v>1.898107941375528</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.881821647052874</v>
+        <v>2.833073330409796</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.95167968274734</v>
+        <v>5.895264541165162</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.719055316210977</v>
+        <v>3.692124745866742</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.535680281537367</v>
+        <v>1.538172849453666</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.509526762998156</v>
+        <v>1.787217711469033</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 85.26</t>
+          <t>X &gt; 85.25</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>322</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.238680005689631</v>
+        <v>-1.267875800042262</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3653940490640224</v>
+        <v>-0.3665808355086781</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.7926295972368465</v>
+        <v>0.7924762072325251</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.096767784303466</v>
+        <v>3.096273291925463</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.179596243630137</v>
+        <v>3.228142163395908</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.855852260842859</v>
+        <v>2.879809669792472</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.180398791899492</v>
+        <v>-0.1311512295057753</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.311414082633632</v>
+        <v>1.384671192413329</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.635408329782038</v>
+        <v>2.734755655076611</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.157415246056004</v>
+        <v>6.25732328207468</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5.881234392200142</v>
+        <v>6.004931013228386</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.908288507830832</v>
+        <v>4.05697805560866</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>4.444583164268558</v>
+        <v>4.61658192383522</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>275</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-2.662734212352532</v>
+        <v>-2.691930006705164</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.092102123598181</v>
+        <v>-2.093288910042837</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.3050553265350331</v>
+        <v>-0.3052087165393544</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.006987998871502</v>
+        <v>2.006493506493499</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.832334809412174</v>
+        <v>1.880880729177946</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.038799748138175</v>
+        <v>1.062757157087788</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.317725752508373</v>
+        <v>1.365737431498694</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.331161073096553</v>
+        <v>-1.281913510702836</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.7896749521988582</v>
+        <v>0.8629320619785545</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.121574337687171</v>
+        <v>2.220921662981745</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>4.825964088517892</v>
+        <v>4.925872124536568</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.496705877236849</v>
+        <v>4.620402498265094</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.89473684210526</v>
+        <v>2.043426389883088</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.120472492331793</v>
+        <v>2.292471251898455</v>
       </c>
     </row>
     <row r="28">
@@ -3361,150 +3361,150 @@
         <v>240</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.064249363867688</v>
+        <v>-2.09344515822032</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.008768790264845</v>
+        <v>-2.009955576709501</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.09645982498010852</v>
+        <v>0.09630643497578717</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.476684968568478</v>
+        <v>1.476190476190474</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.9383954154727832</v>
+        <v>0.986941335238555</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4308972215588014</v>
+        <v>-0.4069398126091883</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7343924191750375</v>
+        <v>0.7824040981653582</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.816009557945037</v>
+        <v>-1.76676199555132</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.456341618865515</v>
+        <v>1.529598728645212</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.106422822535656</v>
+        <v>3.205770147830229</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.235054997608799</v>
+        <v>6.334963033627474</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>5.019433149964129</v>
+        <v>5.143129770992374</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.099282296650713</v>
+        <v>2.247971844428541</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.491684613543917</v>
+        <v>1.66368337311058</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 95.72</t>
+          <t>X &gt; 95.71</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>215</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-3.643706728208777</v>
+        <v>-3.672902522561408</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.929311425923757</v>
+        <v>-2.930498212368413</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.9985014153299687</v>
+        <v>-0.9986548053342901</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.5270725654677051</v>
+        <v>0.5265780730897021</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.01121698762798928</v>
+        <v>0.03732893213778254</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.109191795202214</v>
+        <v>-1.085234386252601</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2636695963288389</v>
+        <v>-0.2156579173385182</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.056319635464419</v>
+        <v>-3.007072073070702</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1385121615011755</v>
+        <v>0.2117692712808719</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.6839422023806137</v>
+        <v>0.783289527675187</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.735054997608799</v>
+        <v>3.834963033627474</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.304316870894354</v>
+        <v>3.428013491922599</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.3716479359074256</v>
+        <v>-0.222958388129598</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.6110285647506615</v>
+        <v>-0.4390298051839991</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 99.21</t>
+          <t>X &gt; 99.2</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>183</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-2.207691986818503</v>
+        <v>-2.236887781171134</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.179533817587249</v>
+        <v>-2.180720604031904</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.3885128526155128</v>
+        <v>-0.3886662426198342</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.8346084658362329</v>
+        <v>0.8341139734582299</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.343025349554537</v>
+        <v>-1.294479429788765</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.04565131991945</v>
+        <v>-1.021693910969837</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.130361679185619</v>
+        <v>-1.082350000195298</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.329670760130831</v>
+        <v>-4.280423197737115</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-2.204860566926826</v>
+        <v>-2.131603457147129</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.508331275824993</v>
+        <v>-2.40898395053042</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.01920800307327397</v>
+        <v>0.1191160390919492</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.05358615542859724</v>
+        <v>0.1772827764568419</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.552357047611579</v>
+        <v>-2.403667499833752</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.780173309953348</v>
+        <v>-1.608174550386686</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>173</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.19189868949389</v>
+        <v>-2.221094483846521</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.912911372153097</v>
+        <v>-0.9140981585977528</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1516133927462917</v>
+        <v>-0.1517667827506131</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.134681115003922</v>
+        <v>1.134186622625919</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.137712484334543</v>
+        <v>-1.089166564568771</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.8403384546994559</v>
+        <v>-0.8163810457498428</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9250488139656241</v>
+        <v>-0.8770371349753034</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-3.704256186076059</v>
+        <v>-3.655008623682342</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.453099614275139</v>
+        <v>-1.379842504495443</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.303018410604999</v>
+        <v>-2.203671085310425</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1955808405414885</v>
+        <v>-0.09567280452281324</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1612026881861652</v>
+        <v>-0.0375060671579206</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.893492269823277</v>
+        <v>-2.744802722045449</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.089721937515826</v>
+        <v>-1.917723177949163</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>153</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.500523873671611</v>
+        <v>-1.529719668024242</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.8098586607155482</v>
+        <v>0.8086718742708925</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.466881046999852</v>
+        <v>4.466386554621849</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.96780718017866</v>
+        <v>2.016353099944432</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.572370752297417</v>
+        <v>3.59632816124703</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.180470850547579</v>
+        <v>2.228482529537899</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.4062126642771844</v>
+        <v>0.4554602266709011</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2.306014821479891</v>
+        <v>2.379271931259588</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.109690796391874</v>
+        <v>2.209038121686447</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.519368723098992</v>
+        <v>4.619276759117668</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.24655733297066</v>
+        <v>3.370253953998905</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.212027394689926</v>
+        <v>0.3607169424677537</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2158317263253693</v>
+        <v>-0.04383296675870696</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>141</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.7078663851442855</v>
+        <v>-0.7370621794969168</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.227046812572034</v>
+        <v>1.225860026127378</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.959935002285086</v>
+        <v>2.959781612280764</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.636259436653582</v>
+        <v>6.635764944275579</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.261090450933771</v>
+        <v>3.309636370699543</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.686124055036942</v>
+        <v>5.710081463986555</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.892193837614748</v>
+        <v>4.940205516605069</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>1.5882457612039</v>
+        <v>1.637493323597617</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.945703320993175</v>
+        <v>3.018960430772871</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.805004382819341</v>
+        <v>2.904351708113914</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.437182657183264</v>
+        <v>5.537090693201939</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.762340951382562</v>
+        <v>4.886037572410807</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.505310665445037</v>
+        <v>1.654000213222865</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.021826457515552</v>
+        <v>1.193825217082214</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>124</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.8680128047279041</v>
+        <v>-0.8972085990805354</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.553059166724395</v>
+        <v>1.55187238027974</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.577642620679043</v>
+        <v>3.577489230674722</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.933674215880302</v>
+        <v>6.933179723502299</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.169578211171711</v>
+        <v>3.218124130937483</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.079855466613246</v>
+        <v>5.103812875562859</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.188693494443854</v>
+        <v>4.236705173434174</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.108721624850666</v>
+        <v>2.157969187244383</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3.660642694134339</v>
+        <v>3.733899803914035</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.617175510707703</v>
+        <v>3.716522836002277</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.638280804060415</v>
+        <v>6.73818884007909</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.672658956415738</v>
+        <v>6.796355577443983</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.026701651489425</v>
+        <v>3.175391199267253</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.252437301715958</v>
+        <v>3.42443606128262</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-3.671392221010542</v>
+        <v>-3.700588015363174</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-2.901625933121991</v>
+        <v>-2.902812719566647</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>0.2748778635472249</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.4052563971399081</v>
+        <v>0.4047619047619051</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-5.872750437967824</v>
+        <v>-5.824738758977503</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-9.911247653183132</v>
+        <v>-9.862000090789415</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-2.488815272702439</v>
+        <v>-2.389467947407866</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-3.079289131920717</v>
+        <v>-2.93059958414289</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.044029672170367</v>
+        <v>-3.872030912603705</v>
       </c>
     </row>
   </sheetData>
@@ -3904,157 +3904,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 15.49</t>
+          <t>X &lt; 15.5</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>12.99527444565613</v>
+        <v>12.9660786513035</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.003135971639914</v>
+        <v>9.001949185195258</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.98931696783726</v>
+        <v>10.98916357783294</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.34315732023467</v>
+        <v>15.39170324000045</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>18.02148373082215</v>
+        <v>18.04544113977177</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.7462971810798</v>
+        <v>16.79430886007012</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>18.66018091824544</v>
+        <v>18.70942848063915</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>17.40872257124647</v>
+        <v>17.48197968102617</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>18.93975615586899</v>
+        <v>19.03910348116356</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>17.54457880713261</v>
+        <v>17.64448684315128</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>19.95990934044031</v>
+        <v>20.08360596146856</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>18.34928229665071</v>
+        <v>18.49797184442854</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>18.57501794687725</v>
+        <v>18.74701670644391</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 18.98</t>
+          <t>X &lt; 18.99</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>190</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>8.045399758939332</v>
+        <v>8.016203964586701</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10.1184241921913</v>
+        <v>10.11723740574664</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>11.30260017585731</v>
+        <v>11.30244678585299</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.48545689839303</v>
+        <v>12.48496240601503</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>15.10506208213945</v>
+        <v>15.15360800190522</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>15.92875190124822</v>
+        <v>15.95270931019783</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17.94930469987679</v>
+        <v>17.99731637886711</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>19.06118342451109</v>
+        <v>19.11043098690481</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>19.526517057462</v>
+        <v>19.5997741672417</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>19.72922984007953</v>
+        <v>19.8285771653741</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>18.47189710287195</v>
+        <v>18.57180513889062</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>19.03259104470097</v>
+        <v>19.15628766572922</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>19.13875598086125</v>
+        <v>19.28744552863908</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>19.36449163108778</v>
+        <v>19.53649039065444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 22.47</t>
+          <t>X &lt; 22.48</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.33303745783774</v>
+        <v>3.417723226659412</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>4.305830692939288</v>
+        <v>4.411865729132423</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.944651039450399</v>
+        <v>5.049055575869261</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.142059645571052</v>
+        <v>7.240795287187041</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.154157689374586</v>
+        <v>8.297937898812435</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.485123450275822</v>
+        <v>9.601651252682913</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>11.72599448635849</v>
+        <v>11.86058279232343</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>12.55091550665446</v>
+        <v>12.68340982575452</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>13.00672921576474</v>
+        <v>13.1619011341435</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>14.74078974760026</v>
+        <v>14.91539214095738</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>13.76089479089045</v>
+        <v>13.93805581713262</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>12.76168121197963</v>
+        <v>12.96529471944597</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>12.85832622429929</v>
+        <v>13.08560071040792</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>14.11765360579198</v>
+        <v>14.36557340747483</v>
       </c>
     </row>
     <row r="9">
@@ -4067,202 +4067,202 @@
         <v>621</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.913608929208003</v>
+        <v>2.884413134855372</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.624484027770585</v>
+        <v>1.623297241325929</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.873835026268353</v>
+        <v>1.873681636264031</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>3.292304936362356</v>
+        <v>3.291810443984353</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.720198958145893</v>
+        <v>3.768744877911665</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.500664775220585</v>
+        <v>4.524622184170198</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.704199182460059</v>
+        <v>5.752210861450379</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>5.398161134486521</v>
+        <v>5.447408696880238</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6.142331957029761</v>
+        <v>6.215589066809457</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.224780310458364</v>
+        <v>7.324127635752937</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>6.536987364758559</v>
+        <v>6.636895400777234</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.927243133861062</v>
+        <v>6.050939754889306</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>5.668122876360854</v>
+        <v>5.816812424138682</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>7.021072697279827</v>
+        <v>7.193071456846489</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 29.44</t>
+          <t>X &lt; 29.45</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>882</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.260580568105105</v>
+        <v>1.483139018757562</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2162878990775567</v>
+        <v>0.2986029818490579</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.0651048008702233</v>
+        <v>0.1916653226120175</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.5186350819471599</v>
+        <v>0.7218639148661694</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.000753692116774</v>
+        <v>1.198805742018216</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.524885091366365</v>
+        <v>1.648112977737725</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.233825525751001</v>
+        <v>2.330629843729717</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.447028990807802</v>
+        <v>2.496276553201518</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.066318943128564</v>
+        <v>3.139576052908261</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.236808310063999</v>
+        <v>3.336155635358573</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.691971097382037</v>
+        <v>2.791879133400712</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.612970564930109</v>
+        <v>2.736667185958353</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.986470505267491</v>
+        <v>3.135160053045318</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>3.77909957953031</v>
+        <v>3.951098339096973</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 32.93</t>
+          <t>X &lt; 32.94</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1129</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.9291814008208306</v>
+        <v>0.9578425210304857</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.6466046965966825</v>
+        <v>0.6518780495353695</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.6947031081215371</v>
+        <v>0.8339933303144065</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.356372007245767</v>
+        <v>1.452716297786715</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.526674128197904</v>
+        <v>1.629378927015352</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.355491913368866</v>
+        <v>2.481067242064533</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.333669065174441</v>
+        <v>3.441642109345111</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.840913973203463</v>
+        <v>3.998844600443967</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.779931816680687</v>
+        <v>3.925708366134167</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.815752612910615</v>
+        <v>3.950607905942327</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.725311862090635</v>
+        <v>2.861511706193845</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.025411892213903</v>
+        <v>3.149108513242147</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.402426672204307</v>
+        <v>3.551116219982134</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.982458159454744</v>
+        <v>4.154456919021406</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 36.42</t>
+          <t>X &lt; 36.43</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1386</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.520525930532699</v>
+        <v>1.56714139399714</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8141027826067244</v>
+        <v>0.8100754421404091</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.2028811814014659</v>
+        <v>0.2407667979175301</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8381568300403401</v>
+        <v>0.9116743471582183</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.165668142745503</v>
+        <v>1.179432966037218</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.607342316680736</v>
+        <v>1.707800555900029</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.099832534615146</v>
+        <v>2.190450075176855</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.642864900929425</v>
+        <v>2.771939178663878</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.942633105157007</v>
+        <v>3.064370910899406</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.030665246778085</v>
+        <v>3.146374899450095</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.320913583467387</v>
+        <v>2.480496174837846</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.427441807972777</v>
+        <v>2.58094519997578</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.584491531859953</v>
+        <v>2.733181079637781</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.026677398536698</v>
+        <v>3.19867615810336</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1687</v>
+        <v>1690</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6237557613047997</v>
+        <v>0.6626261304596639</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5824540894195707</v>
+        <v>0.5804324303451693</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5427122904633492</v>
+        <v>0.5717966310542195</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.8504522269511128</v>
+        <v>0.9106617337929848</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.8447070525536517</v>
+        <v>0.8662110643316012</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.023737886922461</v>
+        <v>1.11289911883847</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.412400308721388</v>
+        <v>1.497812903196802</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1.832905629431686</v>
+        <v>1.950052163740715</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.416893887110092</v>
+        <v>1.533534187126129</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.809578641076094</v>
+        <v>1.924513995044251</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.486534287549631</v>
+        <v>1.636381473343789</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.791931669798345</v>
+        <v>1.906139824215316</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.176296514660187</v>
+        <v>2.255368294132687</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.67401024089029</v>
+        <v>2.681927949047456</v>
       </c>
     </row>
     <row r="14">
@@ -4324,153 +4324,153 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2007</v>
+        <v>2018</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.09334139520822049</v>
+        <v>0.1240585345418737</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.05545031577252502</v>
+        <v>-0.05388004304776217</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.02254175428305416</v>
+        <v>0.02258374728069867</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.03105614688610814</v>
+        <v>0.0314173006480587</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.03382680674943828</v>
+        <v>-0.08566185502620982</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.4396569554469849</v>
+        <v>0.4115860182562372</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6801885131836372</v>
+        <v>0.6249966907579534</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7373933233266996</v>
+        <v>0.6805370821825463</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.8035914531928796</v>
+        <v>0.7205692344946115</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4787914616869884</v>
+        <v>0.3694694554464562</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2027166891510888</v>
+        <v>0.09424061898126013</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.6136342450363017</v>
+        <v>0.4772881868339454</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.919003412188566</v>
+        <v>0.7540392045077837</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.57202841025542</v>
+        <v>1.37833484321299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 46.88</t>
+          <t>X &lt; 46.89</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2291</v>
+        <v>2302</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7448049194232382</v>
+        <v>-0.7174552374139793</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.5532397701461633</v>
+        <v>-0.5496415461707542</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.6641106934096968</v>
+        <v>-0.6608271577609131</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6843319805840622</v>
+        <v>-0.6806722689075713</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6775466135127246</v>
+        <v>-0.7139817860653537</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.3565895515573558</v>
+        <v>-0.3744722801416529</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.06956754601208104</v>
+        <v>-0.1084938374489113</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.0775100658539003</v>
+        <v>-0.1174263514149843</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1580602394387753</v>
+        <v>-0.2172586619052836</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.6789802275732768</v>
+        <v>-0.7570803870064253</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.033907513289194</v>
+        <v>-1.110807031448445</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.8446095888060441</v>
+        <v>-0.941939673452076</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.367995190260288</v>
+        <v>-0.488133235901465</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.3187979556070601</v>
+        <v>0.1762087133943879</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 50.37</t>
+          <t>X &lt; 50.38</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2559</v>
+        <v>2570</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.4980233400211347</v>
+        <v>-0.4775914996837258</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4553848929486293</v>
+        <v>-0.4527002191055729</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.5958229246956321</v>
+        <v>-0.5931873013021374</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7949512063374584</v>
+        <v>-0.7912513842746378</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6893304412250458</v>
+        <v>-0.7168844370246035</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4097960658647324</v>
+        <v>-0.4231022124023056</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1226483706405048</v>
+        <v>-0.1523068059867541</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.06162359303275622</v>
+        <v>-0.09233135372937795</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.3351300400008341</v>
+        <v>-0.3797863846233867</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.6954369771782183</v>
+        <v>-0.7549913129312316</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.112720178035232</v>
+        <v>-1.170866737068209</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.9396648586262728</v>
+        <v>-1.013557631807018</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.4788427033492795</v>
+        <v>-0.5704840093248649</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1139230456979732</v>
+        <v>-0.2218548888868312</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2764</v>
+        <v>2775</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2662959369081364</v>
+        <v>-0.2504274633374877</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.3096813743186431</v>
+        <v>-0.307856545493145</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2166032380829463</v>
+        <v>-0.2156701144379412</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4633534837266495</v>
+        <v>-0.4612721210566875</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4773396488378339</v>
+        <v>-0.5001276302786906</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4128597035212849</v>
+        <v>-0.4234088508173528</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.08104725362660758</v>
+        <v>-0.1051468244323033</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.08531414843281482</v>
+        <v>0.05991905443070067</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.0442795025780427</v>
+        <v>0.006816954064873926</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2076426880616467</v>
+        <v>-0.2574060546406898</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.4282988151848386</v>
+        <v>-0.4774919699722417</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.26527400838728</v>
+        <v>-0.3272519358855561</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.0865224049767761</v>
+        <v>-0.1619705186838516</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1958573101189245</v>
+        <v>0.1073770668042684</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2982</v>
+        <v>2993</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.02682588028392985</v>
+        <v>-0.01510184484706656</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.08291457646862455</v>
+        <v>0.08308380210358735</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.07376798847270294</v>
+        <v>0.07355898712847875</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.279108257812986</v>
+        <v>-0.2778887778887835</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.4315477473490148</v>
+        <v>-0.4493233771753964</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.4838515136435291</v>
+        <v>-0.4916338035011165</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3162655489302395</v>
+        <v>-0.334262568501309</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.062328165709431</v>
+        <v>-0.08175588240249709</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4396521318319486</v>
+        <v>-0.4672880847859631</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.4004983652294598</v>
+        <v>-0.4387076633142399</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6870555551550197</v>
+        <v>-0.7244495164392859</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3324435256390927</v>
+        <v>-0.3806598784233302</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1639594063328573</v>
+        <v>-0.222803038670996</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.0198848029550831</v>
+        <v>-0.08859973191225379</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3122</v>
+        <v>3133</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.07262256960931524</v>
+        <v>-0.0625593773345372</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.07168093661668706</v>
+        <v>-0.07103135837351715</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1938636136835754</v>
+        <v>-0.1931337685865557</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3975168194264143</v>
+        <v>-0.3959592745784306</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4394923733060949</v>
+        <v>-0.4542850598388881</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.5400559010050188</v>
+        <v>-0.546226663930419</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4476945095561931</v>
+        <v>-0.4622880462083145</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1621306150635391</v>
+        <v>-0.1781456633860827</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3654257833304086</v>
+        <v>-0.3888206467531248</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.1101478748411822</v>
+        <v>-0.1432363339464047</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2649450023911939</v>
+        <v>-0.2976900275970138</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.1394715622560554</v>
+        <v>0.09727650145489264</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1216165905988333</v>
+        <v>0.07104140409669668</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.2053830974217732</v>
+        <v>0.1466336869737503</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3267</v>
+        <v>3278</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.0190839694656475</v>
+        <v>0.02711090376692482</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.2232379190977696</v>
+        <v>0.2228205124495588</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1854702136613327</v>
+        <v>-0.1848073787467115</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4353789109961639</v>
+        <v>-0.4337851929092906</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4382834612060975</v>
+        <v>-0.4502861264793268</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.5822967126529406</v>
+        <v>-0.5869966192636866</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4977904356406881</v>
+        <v>-0.5094528272532202</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.03171380481335717</v>
+        <v>-0.04528412303812246</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.289787150490632</v>
+        <v>-0.3091666282438155</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.06938012407443495</v>
+        <v>0.04154101925010423</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2098991308315732</v>
+        <v>-0.2369662562231767</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.2393016112672726</v>
+        <v>0.2041053807484658</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1730277066874351</v>
+        <v>0.1310916980424537</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1406745125338063</v>
+        <v>0.09234922627307185</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3359</v>
+        <v>3370</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.06949915333278511</v>
+        <v>0.07634989547955939</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1351301516910439</v>
+        <v>0.1349783874142858</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2138764757122757</v>
+        <v>-0.2131434319274916</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.4830953816838317</v>
+        <v>-0.4814032121724523</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.5006386304496218</v>
+        <v>-0.5107897489086284</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.5138098044713786</v>
+        <v>-0.5179522460017196</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4636170876580081</v>
+        <v>-0.4737650855282567</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.02304274268995954</v>
+        <v>-0.03492945210739862</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2757233831162509</v>
+        <v>-0.2926234935770111</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.09830509896300299</v>
+        <v>-0.1221294767498904</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3458492260675854</v>
+        <v>-0.3690096909500511</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.0324501092024434</v>
+        <v>0.002263816069472568</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.04357484620643248</v>
+        <v>-0.07960157592150807</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.1582359977491379</v>
+        <v>-0.1995708306480779</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3462</v>
+        <v>3473</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.2672854083145637</v>
+        <v>0.2724469817682049</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1969019063384891</v>
+        <v>0.1965245763273131</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1534441965190751</v>
+        <v>-0.1529281612737279</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4395976735206162</v>
+        <v>-0.4381075427587078</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3285305424644136</v>
+        <v>-0.3374890687438352</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.303615761424318</v>
+        <v>-0.307590966492171</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.3150214368833844</v>
+        <v>-0.3239177409151068</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1274737177181677</v>
+        <v>0.1169210551337372</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.06178163851358676</v>
+        <v>-0.07668840955682299</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.001386371540121445</v>
+        <v>-0.02186862122355393</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2764890139352119</v>
+        <v>-0.2962222367983003</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.03386733010268728</v>
+        <v>0.008237684661423827</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.06311423427705165</v>
+        <v>0.03222630614414612</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.04138875445146795</v>
+        <v>-0.07676676605825605</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3561</v>
+        <v>3572</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.289089565436548</v>
+        <v>0.2932354554477357</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.204007588128654</v>
+        <v>0.2035860899571631</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.04840084774980369</v>
+        <v>0.04827871146662943</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3101627864954679</v>
+        <v>-0.3091249900295239</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3291115873283417</v>
+        <v>-0.3364785660925449</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3806964183459485</v>
+        <v>-0.3836623451976351</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.338103843904193</v>
+        <v>-0.345355052435373</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.1352099542500866</v>
+        <v>0.1262881255591708</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.07852471128965277</v>
+        <v>-0.09093989776425104</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2117164949023902</v>
+        <v>-0.2282343264427027</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.4288058329187052</v>
+        <v>-0.4447572460928058</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.1542266872517146</v>
+        <v>-0.1751410739992423</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1375228689865722</v>
+        <v>-0.1628174083002634</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1767371780876488</v>
+        <v>-0.2059508187520649</v>
       </c>
     </row>
     <row r="24">
@@ -4844,153 +4844,153 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3657</v>
+        <v>3668</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.3256234790024379</v>
+        <v>0.3287906472673185</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.2278760720954693</v>
+        <v>0.2273632638702026</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.120541976924855</v>
+        <v>0.1202033272472462</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1433950241594673</v>
+        <v>-0.142895983842152</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2850088398463697</v>
+        <v>-0.2910479676351656</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2183005867247871</v>
+        <v>-0.2210493519635577</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.1517065619021167</v>
+        <v>-0.1580720923108316</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1878124458769719</v>
+        <v>0.1802530652361938</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.03271154422506584</v>
+        <v>0.02220241319008665</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.09192917600754669</v>
+        <v>-0.1057766931283695</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3633056581289011</v>
+        <v>-0.376423509548772</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.1496704302490457</v>
+        <v>-0.166815733094829</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.03508074326180832</v>
+        <v>-0.05613009070363972</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.09465664978668542</v>
+        <v>-0.1188502510261031</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 81.77</t>
+          <t>X &lt; 81.76</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3761</v>
+        <v>3771</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.03630707492404639</v>
+        <v>0.02688606094810808</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.05579079980494583</v>
+        <v>0.04363945368965005</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.0860251520435682</v>
+        <v>-0.09781484124490447</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2595918810735256</v>
+        <v>-0.2709222805758174</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3326037003539142</v>
+        <v>-0.3490375007402804</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2330109564133167</v>
+        <v>-0.2470650662036178</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.2236755213769825</v>
+        <v>-0.2404033837474771</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.01391699722707074</v>
+        <v>-0.003457785861094465</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.08552419809323908</v>
+        <v>-0.1052882770045116</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.203670138951729</v>
+        <v>-0.1993071148629255</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5529365007971521</v>
+        <v>-0.5476548784021986</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.317731346448312</v>
+        <v>-0.3157226011253158</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.08506113769272616</v>
+        <v>-0.08633356384293478</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.08358348891110978</v>
+        <v>-0.1140281092548463</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 85.26</t>
+          <t>X &lt; 85.25</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3836</v>
+        <v>3847</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.1041710050593068</v>
+        <v>0.1064684859938509</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.09188956039350415</v>
+        <v>0.09173311638888038</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.08084283510133616</v>
+        <v>-0.08059869721705581</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2484840381917977</v>
+        <v>-0.2477313974591766</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2525452000452049</v>
+        <v>-0.2561430354391874</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.201101869494984</v>
+        <v>-0.2026596569671639</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.141550854309223</v>
+        <v>-0.1454198077332833</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.05627918055921555</v>
+        <v>0.05173441417269942</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.01636514152674806</v>
+        <v>-0.02284156211283772</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.1227438441310156</v>
+        <v>-0.1312418836767364</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.4431164011929667</v>
+        <v>-0.4507512520868104</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.4202489761432204</v>
+        <v>-0.4300710603924145</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.2524899212278413</v>
+        <v>-0.2650219185652247</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2988089561467362</v>
+        <v>-0.3132900260749452</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3883</v>
+        <v>3894</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1884884869194465</v>
+        <v>0.1901697210562006</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2082829855160639</v>
+        <v>0.2077863587743636</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.007219968791105202</v>
+        <v>0.007211257852439701</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1311153568018497</v>
+        <v>-0.1307084309133515</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1159040021359914</v>
+        <v>-0.1192590234598825</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.0357545847045202</v>
+        <v>-0.03747116405288864</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.02931794929111931</v>
+        <v>-0.03287830805527392</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1347918477290904</v>
+        <v>0.1306739018845704</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.03658853244576221</v>
+        <v>0.03092385474592874</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.05304034528871426</v>
+        <v>-0.06043474356706469</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2690623467041249</v>
+        <v>-0.2758914698367292</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2460108654798958</v>
+        <v>-0.2547141715127736</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.05957455195896699</v>
+        <v>-0.07070594761253801</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.07679765961258767</v>
+        <v>-0.08965509632958657</v>
       </c>
     </row>
     <row r="28">
@@ -5052,153 +5052,153 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3918</v>
+        <v>3929</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1265629824394452</v>
+        <v>0.1281428681622288</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1827070367071641</v>
+        <v>0.1822756674755581</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.02008806676502672</v>
+        <v>-0.02002182221541204</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.07966262138400282</v>
+        <v>-0.07940739128857643</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.04390659624099413</v>
+        <v>-0.04700144451428656</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.06366891870271019</v>
+        <v>0.06190279174269619</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.01836269518352651</v>
+        <v>0.01512767540112492</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1513706663159198</v>
+        <v>0.1476810370619788</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.002522262930433783</v>
+        <v>-0.002345009704214363</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.09390014193824925</v>
+        <v>-0.1002303606874406</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3098315109349343</v>
+        <v>-0.3155964780714129</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.2356688908522031</v>
+        <v>-0.2432223022714268</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.0546472772201696</v>
+        <v>-0.06436912249257887</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.01865229304107885</v>
+        <v>-0.0300257980101506</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 95.72</t>
+          <t>X &lt; 95.71</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3943</v>
+        <v>3954</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1985581858458332</v>
+        <v>0.1997444897084293</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.2188966121793143</v>
+        <v>0.2183601065986167</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.04018769549098522</v>
+        <v>0.04008533367272094</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.01817125876941361</v>
+        <v>-0.01809139397434478</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.01396896473053744</v>
+        <v>0.01103924086560681</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.09745003230098348</v>
+        <v>0.09575243036574221</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.07721942339443899</v>
+        <v>0.07414439943607221</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2064433837279651</v>
+        <v>0.2029349741456414</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.08349460772063111</v>
+        <v>0.07889568915712175</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.05832722250187317</v>
+        <v>0.05224142962237721</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.132152300921355</v>
+        <v>-0.1377435622785086</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1088938462335918</v>
+        <v>-0.1159703301198647</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.09370420334442287</v>
+        <v>0.08457108589503548</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1055784338161203</v>
+        <v>0.09501872971148373</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 99.21</t>
+          <t>X &lt; 99.2</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3975</v>
+        <v>3986</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1018322141998453</v>
+        <v>0.1030414634350976</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1592146559353083</v>
+        <v>0.1588371529886743</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.003844002936290281</v>
+        <v>0.003841252755798052</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.02791561696059119</v>
+        <v>-0.02781352781352808</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.07494160021173002</v>
+        <v>0.07225631229320584</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0848363126281626</v>
+        <v>0.08337899894146972</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1143103833471386</v>
+        <v>0.1115425905269944</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2387505525799511</v>
+        <v>0.2355760138007099</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.1916850024501144</v>
+        <v>0.187412142158955</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2101758593120664</v>
+        <v>0.204517014998153</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.06989662656807383</v>
+        <v>0.06459452021559287</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.06815077631564748</v>
+        <v>0.06163528754201764</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.1903285743167089</v>
+        <v>0.182195571541655</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1536342990785045</v>
+        <v>0.1444075744820381</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3985</v>
+        <v>3996</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.09537211353768527</v>
+        <v>0.09652324620306274</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.09854085863850059</v>
+        <v>0.09832785642422692</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.007394028873747516</v>
+        <v>-0.007366304396974499</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.03875099305021479</v>
+        <v>-0.03862064046786884</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.06249823637079288</v>
+        <v>0.05997504310371937</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.07310979071267809</v>
+        <v>0.07174816607879819</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1022948907849184</v>
+        <v>0.0996869693452993</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.2001935657499416</v>
+        <v>0.1972559954531761</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1530834735021074</v>
+        <v>0.1491105173646972</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1944565820409707</v>
+        <v>0.1891034811635635</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.07908709389766244</v>
+        <v>0.07402279856870564</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.07743415322472202</v>
+        <v>0.0712188155146265</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.198253696550367</v>
+        <v>0.1904912339707039</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1622199544054723</v>
+        <v>0.1534231128503123</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4005</v>
+        <v>4016</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.05766037563786597</v>
+        <v>0.05876382663945634</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.02788791872195873</v>
+        <v>0.02786302640205207</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.05460259201856132</v>
+        <v>-0.05444681392744855</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1598862227972333</v>
+        <v>-0.1594280036903015</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.06185371257903682</v>
+        <v>-0.06378330244260866</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.09968200434806818</v>
+        <v>-0.1004454454786412</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.02125729833909418</v>
+        <v>-0.02327574274938371</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.02393060660245538</v>
+        <v>0.02173460647089343</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.001645027011818456</v>
+        <v>-0.001529514743658922</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.01359002965297407</v>
+        <v>0.009252734894900527</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1022703516925958</v>
+        <v>-0.1063158914782676</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.05387605892033065</v>
+        <v>-0.05908526136203562</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.06420990523783132</v>
+        <v>0.05759345259384219</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.0793874849546512</v>
+        <v>0.07171790166303538</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4017</v>
+        <v>4028</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.02528744341105948</v>
+        <v>0.02638904123526231</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01561691338370252</v>
+        <v>0.01562198104627299</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1174594070622632</v>
+        <v>-0.1171333603530869</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2220568574392985</v>
+        <v>-0.2214321092478642</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.1010978781188712</v>
+        <v>-0.1027704969800922</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1627812795298098</v>
+        <v>-0.163299244389826</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1097096351655864</v>
+        <v>-0.1113381571010592</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.01635755695075858</v>
+        <v>-0.01829066849794003</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.01390535610547516</v>
+        <v>-0.01681006547000408</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.004536308692060231</v>
+        <v>-0.008515566455479018</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1206663954260279</v>
+        <v>-0.1243522727481192</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.09720034095401786</v>
+        <v>-0.1019074498513035</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.0192673638483285</v>
+        <v>0.01323617801008226</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.03506275643661638</v>
+        <v>0.0280494770496631</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4034</v>
+        <v>4045</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.02711460944587429</v>
+        <v>0.02808433085476025</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.01071547402910511</v>
+        <v>0.01072883706093819</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1234618890701569</v>
+        <v>-0.1231215729137602</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2023456941417123</v>
+        <v>-0.201779108684164</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.08415384662632164</v>
+        <v>-0.08566185502620982</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1195826907984525</v>
+        <v>-0.1201152382198458</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.06707998864481368</v>
+        <v>-0.06861597422687993</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.02558051504074399</v>
+        <v>-0.02727380333541163</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.02339759050973811</v>
+        <v>-0.02595682691033829</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.01764849990119188</v>
+        <v>-0.02115831187175132</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1341548116555131</v>
+        <v>-0.1373689821828066</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1354231433956414</v>
+        <v>-0.1394869821581111</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.02122575787221592</v>
+        <v>-0.02649676654525734</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.02934496834338063</v>
+        <v>-0.0354307595635035</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4074</v>
+        <v>4085</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.0759716621497617</v>
+        <v>0.07651579834385558</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.117393715853602</v>
+        <v>0.1171089420440552</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.01930924886729457</v>
+        <v>-0.01925346085754143</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.00182372142515419</v>
+        <v>0.001831501831496496</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1136342104764552</v>
+        <v>0.1120838201758545</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1305105850719386</v>
+        <v>0.1295452431771196</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.1817296731160596</v>
+        <v>0.1800091812543059</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.242813971466731</v>
+        <v>0.2408970935059571</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.195411652370467</v>
+        <v>0.193005411611793</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1437777350744796</v>
+        <v>0.1408398470231873</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.02644572608561901</v>
+        <v>0.0238084348016443</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.02556661414469374</v>
+        <v>0.02231988599113777</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1345583702703408</v>
+        <v>0.1303751728671116</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.1533193705394922</v>
+        <v>0.1484854946936096</v>
       </c>
     </row>
   </sheetData>
